--- a/data/dados_tratados.xlsx
+++ b/data/dados_tratados.xlsx
@@ -8,24 +8,38 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaike\OneDrive\Documentos\GitHub\analise-vendas-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB6E3192-A080-40BD-B095-EC3E0D9920E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E82B7F-B388-4B88-AEDA-F6ECEA6C729D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Tratados" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dados Tratados'!$A$1:$G$121</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="174">
   <si>
     <t>Data</t>
   </si>
@@ -48,9 +62,6 @@
     <t>Receita</t>
   </si>
   <si>
-    <t>03-08-2023</t>
-  </si>
-  <si>
     <t>Monitor</t>
   </si>
   <si>
@@ -63,9 +74,6 @@
     <t>40810.25</t>
   </si>
   <si>
-    <t>2023-04-25</t>
-  </si>
-  <si>
     <t>Notebook</t>
   </si>
   <si>
@@ -75,69 +83,39 @@
     <t>Carlos</t>
   </si>
   <si>
-    <t>2023-02-09 00:00:00</t>
-  </si>
-  <si>
     <t>sul</t>
   </si>
   <si>
     <t>Daniela</t>
   </si>
   <si>
-    <t>2023-07-04 00:00:00</t>
-  </si>
-  <si>
     <t>Teclado</t>
   </si>
   <si>
     <t xml:space="preserve"> Sudeste </t>
   </si>
   <si>
-    <t>01-17-2023</t>
-  </si>
-  <si>
     <t>Headset</t>
   </si>
   <si>
     <t>Bruno</t>
   </si>
   <si>
-    <t>R$ 760.94</t>
-  </si>
-  <si>
-    <t>2023-12-28</t>
-  </si>
-  <si>
     <t>CENTRO-OESTE</t>
   </si>
   <si>
-    <t>2023-10-26 00:00:00</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Sul </t>
   </si>
   <si>
     <t>11 unidades</t>
   </si>
   <si>
-    <t>2465,45</t>
-  </si>
-  <si>
     <t>46843.55</t>
   </si>
   <si>
-    <t>2023-01-07</t>
-  </si>
-  <si>
     <t>1 unidades</t>
   </si>
   <si>
-    <t>758,5</t>
-  </si>
-  <si>
-    <t>12-03-2023</t>
-  </si>
-  <si>
     <t>centro-oeste</t>
   </si>
   <si>
@@ -147,48 +125,27 @@
     <t>10834.45</t>
   </si>
   <si>
-    <t>2023-12-16 00:00:00</t>
-  </si>
-  <si>
     <t>Ana</t>
   </si>
   <si>
     <t>3 unidades</t>
   </si>
   <si>
-    <t>2649,97</t>
-  </si>
-  <si>
-    <t>2023-01-12</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Centro-Oeste </t>
   </si>
   <si>
     <t>6 unidades</t>
   </si>
   <si>
-    <t>1855,07</t>
-  </si>
-  <si>
-    <t>14/02/2023</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Nordeste </t>
   </si>
   <si>
     <t>2 unidades</t>
   </si>
   <si>
-    <t>4836,45</t>
-  </si>
-  <si>
     <t>91892.55</t>
   </si>
   <si>
-    <t>2023-07-24 00:00:00</t>
-  </si>
-  <si>
     <t>5 unidades</t>
   </si>
   <si>
@@ -198,12 +155,6 @@
     <t>51987.0</t>
   </si>
   <si>
-    <t>2023-01-11</t>
-  </si>
-  <si>
-    <t>4133,85</t>
-  </si>
-  <si>
     <t>37204.65</t>
   </si>
   <si>
@@ -213,30 +164,18 @@
     <t>R$ 2905.81</t>
   </si>
   <si>
-    <t>2023-04-21 00:00:00</t>
-  </si>
-  <si>
-    <t>09-19-2023</t>
-  </si>
-  <si>
     <t>865,64</t>
   </si>
   <si>
     <t>5193.84</t>
   </si>
   <si>
-    <t>2023-09-08 00:00:00</t>
-  </si>
-  <si>
     <t>19 unidades</t>
   </si>
   <si>
     <t>R$ 2275.71</t>
   </si>
   <si>
-    <t>2023-04-20</t>
-  </si>
-  <si>
     <t>sudeste</t>
   </si>
   <si>
@@ -246,18 +185,12 @@
     <t>192,09</t>
   </si>
   <si>
-    <t>07/07/2023</t>
-  </si>
-  <si>
     <t>8 unidades</t>
   </si>
   <si>
     <t>1582,95</t>
   </si>
   <si>
-    <t>2023-02-22 00:00:00</t>
-  </si>
-  <si>
     <t>NORDESTE</t>
   </si>
   <si>
@@ -270,9 +203,6 @@
     <t>14855.8</t>
   </si>
   <si>
-    <t>20/12/2023</t>
-  </si>
-  <si>
     <t>Mouse</t>
   </si>
   <si>
@@ -285,27 +215,18 @@
     <t>97991.8</t>
   </si>
   <si>
-    <t>19/05/2023</t>
-  </si>
-  <si>
     <t>SUL</t>
   </si>
   <si>
     <t>R$ 717.83</t>
   </si>
   <si>
-    <t>14/06/2023</t>
-  </si>
-  <si>
     <t>14 unidades</t>
   </si>
   <si>
     <t>R$ 2077.83</t>
   </si>
   <si>
-    <t>14/07/2023</t>
-  </si>
-  <si>
     <t>17 unidades</t>
   </si>
   <si>
@@ -315,9 +236,6 @@
     <t>6717.87</t>
   </si>
   <si>
-    <t>2023-10-06 00:00:00</t>
-  </si>
-  <si>
     <t>nordeste</t>
   </si>
   <si>
@@ -327,12 +245,6 @@
     <t>1087,75</t>
   </si>
   <si>
-    <t>10/02/2023</t>
-  </si>
-  <si>
-    <t>26/09/2023</t>
-  </si>
-  <si>
     <t>13 unidades</t>
   </si>
   <si>
@@ -342,54 +254,30 @@
     <t>3123.27</t>
   </si>
   <si>
-    <t>06-24-2023</t>
-  </si>
-  <si>
     <t>R$ 4913.28</t>
   </si>
   <si>
-    <t>03-27-2023</t>
-  </si>
-  <si>
     <t>R$ 1390.01</t>
   </si>
   <si>
-    <t>26/05/2023</t>
-  </si>
-  <si>
     <t>R$ 3523.1</t>
   </si>
   <si>
     <t>10569.3</t>
   </si>
   <si>
-    <t>2023-06-29 00:00:00</t>
-  </si>
-  <si>
     <t>83244.24</t>
   </si>
   <si>
-    <t>16/02/2023</t>
-  </si>
-  <si>
     <t>R$ 3596.45</t>
   </si>
   <si>
     <t>R$ 1401.69</t>
   </si>
   <si>
-    <t>05-22-2023</t>
-  </si>
-  <si>
     <t>R$ 2415.07</t>
   </si>
   <si>
-    <t>2023-06-14 00:00:00</t>
-  </si>
-  <si>
-    <t>2023-01-28 00:00:00</t>
-  </si>
-  <si>
     <t>SUDESTE</t>
   </si>
   <si>
@@ -399,342 +287,180 @@
     <t>17154.55</t>
   </si>
   <si>
-    <t>2023-04-04 00:00:00</t>
-  </si>
-  <si>
     <t>6772.8</t>
   </si>
   <si>
-    <t>19/10/2023</t>
-  </si>
-  <si>
     <t>R$ 3629.92</t>
   </si>
   <si>
-    <t>2023-10-27 00:00:00</t>
-  </si>
-  <si>
     <t>636,05</t>
   </si>
   <si>
     <t>6360.5</t>
   </si>
   <si>
-    <t>14/08/2023</t>
-  </si>
-  <si>
-    <t>2023-05-23 00:00:00</t>
-  </si>
-  <si>
     <t>3710,43</t>
   </si>
   <si>
-    <t>04-11-2023</t>
-  </si>
-  <si>
     <t>1012,69</t>
   </si>
   <si>
-    <t>2023-03-14</t>
-  </si>
-  <si>
-    <t>25/07/2023</t>
-  </si>
-  <si>
     <t>384,76</t>
   </si>
   <si>
     <t>4617.12</t>
   </si>
   <si>
-    <t>2023-10-20 00:00:00</t>
-  </si>
-  <si>
     <t>R$ 550.23</t>
   </si>
   <si>
-    <t>2023-12-13</t>
-  </si>
-  <si>
     <t>2683,74</t>
   </si>
   <si>
-    <t>08-02-2023</t>
-  </si>
-  <si>
     <t>R$ 4961.6</t>
   </si>
   <si>
-    <t>2023-08-10 00:00:00</t>
-  </si>
-  <si>
     <t>R$ 3624.34</t>
   </si>
   <si>
-    <t>18/02/2023</t>
-  </si>
-  <si>
-    <t>02-20-2023</t>
-  </si>
-  <si>
-    <t>12-20-2023</t>
-  </si>
-  <si>
     <t>R$ 482.06</t>
   </si>
   <si>
-    <t>12-14-2023</t>
-  </si>
-  <si>
     <t>R$ 1424.69</t>
   </si>
   <si>
-    <t>13/09/2023</t>
-  </si>
-  <si>
     <t>3822,16</t>
   </si>
   <si>
-    <t>09-25-2023</t>
-  </si>
-  <si>
     <t>90,35</t>
   </si>
   <si>
-    <t>2023-11-12</t>
-  </si>
-  <si>
     <t>1966,9</t>
   </si>
   <si>
-    <t>2023-08-08</t>
-  </si>
-  <si>
     <t>1211.28</t>
   </si>
   <si>
-    <t>2023-04-12</t>
-  </si>
-  <si>
     <t>9919.56</t>
   </si>
   <si>
-    <t>2023-08-23 00:00:00</t>
-  </si>
-  <si>
     <t>R$ 4615.97</t>
   </si>
   <si>
     <t>9231.94</t>
   </si>
   <si>
-    <t>2023-02-08</t>
-  </si>
-  <si>
-    <t>08-31-2023</t>
-  </si>
-  <si>
     <t>3407,04</t>
   </si>
   <si>
     <t>10221.12</t>
   </si>
   <si>
-    <t>2023-10-19</t>
-  </si>
-  <si>
-    <t>2023-05-06</t>
-  </si>
-  <si>
-    <t>2023-08-17</t>
-  </si>
-  <si>
     <t>R$ 807.99</t>
   </si>
   <si>
-    <t>05/01/2023</t>
-  </si>
-  <si>
     <t>2331,2</t>
   </si>
   <si>
-    <t>2023-12-31</t>
-  </si>
-  <si>
     <t>2293,25</t>
   </si>
   <si>
-    <t>02-02-2023</t>
-  </si>
-  <si>
     <t>15 unidades</t>
   </si>
   <si>
     <t>R$ 3908.7</t>
   </si>
   <si>
-    <t>2023-07-21 00:00:00</t>
-  </si>
-  <si>
     <t>R$ 2016.18</t>
   </si>
   <si>
     <t>10080.9</t>
   </si>
   <si>
-    <t>2023-09-18</t>
-  </si>
-  <si>
     <t>1077,94</t>
   </si>
   <si>
-    <t>2023-09-27 00:00:00</t>
-  </si>
-  <si>
     <t>2196,89</t>
   </si>
   <si>
-    <t>2023-05-16 00:00:00</t>
-  </si>
-  <si>
     <t>R$ 3923.26</t>
   </si>
   <si>
-    <t>12-26-2023</t>
-  </si>
-  <si>
     <t>R$ 2643.65</t>
   </si>
   <si>
     <t>37011.1</t>
   </si>
   <si>
-    <t>2023-08-31</t>
-  </si>
-  <si>
     <t>R$ 3587.68</t>
   </si>
   <si>
     <t>21526.08</t>
   </si>
   <si>
-    <t>01-18-2023</t>
-  </si>
-  <si>
     <t>3728,53</t>
   </si>
   <si>
-    <t>10-12-2023</t>
-  </si>
-  <si>
     <t>R$ 313.21</t>
   </si>
   <si>
-    <t>24/05/2023</t>
-  </si>
-  <si>
     <t>R$ 295.97</t>
   </si>
   <si>
-    <t>12/06/2023</t>
-  </si>
-  <si>
     <t>R$ 1882.81</t>
   </si>
   <si>
     <t>24476.53</t>
   </si>
   <si>
-    <t>07/10/2023</t>
-  </si>
-  <si>
     <t>27818.31</t>
   </si>
   <si>
-    <t>2023-03-31</t>
-  </si>
-  <si>
     <t>12 unidades</t>
   </si>
   <si>
     <t>4698,22</t>
   </si>
   <si>
-    <t>06-09-2023</t>
-  </si>
-  <si>
     <t>R$ 4513.9</t>
   </si>
   <si>
     <t>85764.1</t>
   </si>
   <si>
-    <t>11-21-2023</t>
-  </si>
-  <si>
     <t>1524,53</t>
   </si>
   <si>
-    <t>05-12-2023</t>
-  </si>
-  <si>
     <t>R$ 3318.1</t>
   </si>
   <si>
-    <t>21/01/2023</t>
-  </si>
-  <si>
     <t>2418,33</t>
   </si>
   <si>
-    <t>2023-02-23 00:00:00</t>
-  </si>
-  <si>
-    <t>2023-04-24</t>
-  </si>
-  <si>
     <t>645,74</t>
   </si>
   <si>
     <t>10331.84</t>
   </si>
   <si>
-    <t>2023-09-13 00:00:00</t>
-  </si>
-  <si>
     <t>111,36</t>
   </si>
   <si>
-    <t>2023-02-24 00:00:00</t>
-  </si>
-  <si>
     <t>R$ 130.11</t>
   </si>
   <si>
-    <t>2023-10-14 00:00:00</t>
-  </si>
-  <si>
     <t>3838,04</t>
   </si>
   <si>
     <t>3838.04</t>
   </si>
   <si>
-    <t>2023-07-26</t>
-  </si>
-  <si>
     <t>1595,86</t>
   </si>
   <si>
     <t>1595.86</t>
   </si>
   <si>
-    <t>2023-07-26 00:00:00</t>
-  </si>
-  <si>
-    <t>2023-04-13 00:00:00</t>
-  </si>
-  <si>
     <t>2787,97</t>
   </si>
   <si>
@@ -747,156 +473,81 @@
     <t>26996.94</t>
   </si>
   <si>
-    <t>11-18-2023</t>
-  </si>
-  <si>
     <t>R$ 1651.42</t>
   </si>
   <si>
-    <t>2023-06-16</t>
-  </si>
-  <si>
     <t>R$ 2505.55</t>
   </si>
   <si>
-    <t>06/04/2023</t>
-  </si>
-  <si>
     <t>4433,57</t>
   </si>
   <si>
-    <t>02/02/2023</t>
-  </si>
-  <si>
-    <t>20/06/2023</t>
-  </si>
-  <si>
     <t>2078,11</t>
   </si>
   <si>
-    <t>2023-03-27</t>
-  </si>
-  <si>
     <t>4 unidades</t>
   </si>
   <si>
     <t>9328.53</t>
   </si>
   <si>
-    <t>2023-11-23 00:00:00</t>
-  </si>
-  <si>
     <t>12563.04</t>
   </si>
   <si>
-    <t>2023-06-09 00:00:00</t>
-  </si>
-  <si>
     <t>R$ 1168.19</t>
   </si>
   <si>
     <t>8177.33</t>
   </si>
   <si>
-    <t>2023-08-12</t>
-  </si>
-  <si>
     <t>R$ 2136.39</t>
   </si>
   <si>
-    <t>08/07/2023</t>
-  </si>
-  <si>
     <t>4775,7</t>
   </si>
   <si>
     <t>33429.9</t>
   </si>
   <si>
-    <t>20/11/2023</t>
-  </si>
-  <si>
     <t>3978,43</t>
   </si>
   <si>
     <t>47741.16</t>
   </si>
   <si>
-    <t>09-04-2023</t>
-  </si>
-  <si>
-    <t>11/04/2023</t>
-  </si>
-  <si>
     <t>179,65</t>
   </si>
   <si>
     <t>2155.8</t>
   </si>
   <si>
-    <t>2023-06-08</t>
-  </si>
-  <si>
     <t>R$ 573.21</t>
   </si>
   <si>
-    <t>10-29-2023</t>
-  </si>
-  <si>
-    <t>2023-12-24 00:00:00</t>
-  </si>
-  <si>
-    <t>2023-11-20 00:00:00</t>
-  </si>
-  <si>
-    <t>02-26-2023</t>
-  </si>
-  <si>
-    <t>1348,91</t>
-  </si>
-  <si>
-    <t>12/03/2023</t>
-  </si>
-  <si>
     <t>51491.52</t>
   </si>
   <si>
-    <t>03/05/2023</t>
-  </si>
-  <si>
     <t>6073.8</t>
   </si>
   <si>
-    <t>10-08-2023</t>
-  </si>
-  <si>
     <t>R$ 1650.85</t>
   </si>
   <si>
     <t>18159.35</t>
   </si>
   <si>
-    <t>2023-01-03 00:00:00</t>
-  </si>
-  <si>
     <t>810,29</t>
   </si>
   <si>
     <t>4861.74</t>
   </si>
   <si>
-    <t>01/06/2023</t>
-  </si>
-  <si>
     <t>R$ 827.4</t>
   </si>
   <si>
     <t>1654.8</t>
   </si>
   <si>
-    <t>27/05/2023</t>
-  </si>
-  <si>
     <t>20 unidades</t>
   </si>
   <si>
@@ -906,13 +557,7 @@
     <t>4587,28</t>
   </si>
   <si>
-    <t>2023-06-03</t>
-  </si>
-  <si>
     <t>22540.76</t>
-  </si>
-  <si>
-    <t>2023-08-16 00:00:00</t>
   </si>
   <si>
     <t>26341.62</t>
@@ -922,8 +567,25 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="167" formatCode="&quot;R$&quot;\ #,##0.00"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -951,8 +613,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1233,385 +904,397 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:I121"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.140625" customWidth="1"/>
+    <col min="2" max="2" width="17.140625" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="18.140625" customWidth="1"/>
+    <col min="6" max="6" width="21" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" customWidth="1"/>
+    <col min="9" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>45141</v>
+      </c>
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
       </c>
       <c r="E2">
         <v>14</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="3">
         <v>3139.25</v>
       </c>
       <c r="G2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>45041</v>
+      </c>
+      <c r="B3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="C3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
       </c>
       <c r="E3">
         <v>13</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="3">
         <v>345.37</v>
       </c>
       <c r="G3">
         <v>6216.66</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>16</v>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>44966</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E4">
         <v>15</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="3">
         <v>825.2</v>
       </c>
       <c r="G4">
         <v>2475.6</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>19</v>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>45111</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E5">
         <v>7</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="3">
         <v>2873.97</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>22</v>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>44943</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E6">
         <v>7</v>
       </c>
-      <c r="F6" t="s">
-        <v>25</v>
+      <c r="F6" s="3">
+        <v>760.94</v>
       </c>
       <c r="G6">
         <v>8370.34</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>26</v>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>45288</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E7">
         <v>19</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="3">
         <v>380.24</v>
       </c>
       <c r="G7">
         <v>3422.16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>28</v>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>45225</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" t="s">
-        <v>31</v>
+        <v>22</v>
+      </c>
+      <c r="F8" s="3">
+        <v>2465.4499999999998</v>
       </c>
       <c r="G8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>33</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>44933</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" t="s">
         <v>24</v>
       </c>
-      <c r="E9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" t="s">
-        <v>35</v>
+      <c r="F9" s="3">
+        <v>758.5</v>
       </c>
       <c r="G9">
         <v>1517</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>36</v>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>44997</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10">
+        <v>26</v>
+      </c>
+      <c r="F10" s="3">
         <v>2166.89</v>
       </c>
-      <c r="G10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>40</v>
+      <c r="G10" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>45276</v>
       </c>
       <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
         <v>20</v>
       </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" t="s">
-        <v>43</v>
+        <v>29</v>
+      </c>
+      <c r="F11" s="3">
+        <v>2649.97</v>
       </c>
       <c r="G11">
         <v>15899.82</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>44</v>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>44938</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E12" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>48</v>
+        <v>31</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1855.07</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>44971</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E13" t="s">
-        <v>50</v>
-      </c>
-      <c r="F13" t="s">
-        <v>51</v>
+        <v>33</v>
+      </c>
+      <c r="F13" s="3">
+        <v>4836.45</v>
       </c>
       <c r="G13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>53</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>45131</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E14" t="s">
-        <v>54</v>
-      </c>
-      <c r="F14" t="s">
-        <v>55</v>
+        <v>35</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="G14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>57</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>44937</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E15">
         <v>11</v>
       </c>
-      <c r="F15" t="s">
-        <v>58</v>
+      <c r="F15" s="3">
+        <v>4133.8500000000004</v>
       </c>
       <c r="G15" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>45111</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" t="s">
         <v>19</v>
-      </c>
-      <c r="B16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" t="s">
-        <v>24</v>
       </c>
       <c r="E16">
         <v>10</v>
       </c>
-      <c r="F16" t="s">
-        <v>61</v>
+      <c r="F16" s="3" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>62</v>
+      <c r="A17" s="1">
+        <v>45037</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D17" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E17">
         <v>17</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="3">
         <v>4668.8900000000003</v>
       </c>
       <c r="G17">
@@ -1619,553 +1302,553 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>63</v>
+      <c r="A18" s="1">
+        <v>45188</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D18" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E18">
         <v>8</v>
       </c>
-      <c r="F18" t="s">
-        <v>64</v>
+      <c r="F18" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="G18" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>66</v>
+      <c r="A19" s="1">
+        <v>45177</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E19" t="s">
-        <v>67</v>
-      </c>
-      <c r="F19" t="s">
-        <v>68</v>
+        <v>43</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>69</v>
+      <c r="A20" s="1">
+        <v>45036</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D20" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E20" t="s">
-        <v>71</v>
-      </c>
-      <c r="F20" t="s">
-        <v>72</v>
+        <v>46</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="G20">
         <v>1152.54</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>73</v>
+      <c r="A21" s="1">
+        <v>45114</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D21" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E21" t="s">
-        <v>74</v>
-      </c>
-      <c r="F21" t="s">
-        <v>75</v>
+        <v>48</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>76</v>
+      <c r="A22" s="1">
+        <v>44979</v>
       </c>
       <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" t="s">
+        <v>51</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G22" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>45280</v>
+      </c>
+      <c r="B23" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" t="s">
         <v>20</v>
       </c>
-      <c r="C22" t="s">
-        <v>77</v>
-      </c>
-      <c r="D22" t="s">
-        <v>41</v>
-      </c>
-      <c r="E22" t="s">
-        <v>78</v>
-      </c>
-      <c r="F22" t="s">
-        <v>79</v>
-      </c>
-      <c r="G22" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>81</v>
-      </c>
-      <c r="B23" t="s">
-        <v>82</v>
-      </c>
-      <c r="C23" t="s">
-        <v>27</v>
-      </c>
       <c r="D23" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E23" t="s">
-        <v>83</v>
-      </c>
-      <c r="F23" t="s">
-        <v>84</v>
+        <v>55</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="G23" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>86</v>
+      <c r="A24" s="1">
+        <v>45065</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C24" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="D24" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E24" t="s">
-        <v>42</v>
-      </c>
-      <c r="F24" t="s">
-        <v>88</v>
+        <v>29</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>89</v>
+      <c r="A25" s="1">
+        <v>45091</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D25" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E25" t="s">
-        <v>90</v>
-      </c>
-      <c r="F25" t="s">
-        <v>91</v>
+        <v>60</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="G25">
         <v>27011.79</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>92</v>
+      <c r="A26" s="1">
+        <v>45121</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C26" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D26" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E26" t="s">
-        <v>93</v>
-      </c>
-      <c r="F26" t="s">
-        <v>94</v>
+        <v>62</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="G26" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>96</v>
+      <c r="A27" s="1">
+        <v>45205</v>
       </c>
       <c r="B27" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C27" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="D27" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E27" t="s">
-        <v>98</v>
-      </c>
-      <c r="F27" t="s">
-        <v>99</v>
+        <v>66</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="G27">
         <v>15228.5</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>100</v>
+      <c r="A28" s="1">
+        <v>44967</v>
       </c>
       <c r="B28" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C28" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="D28" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" t="s">
+        <v>55</v>
+      </c>
+      <c r="F28" s="3">
+        <v>979.88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>45195</v>
+      </c>
+      <c r="B29" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29" t="s">
+        <v>68</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G29" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>45101</v>
+      </c>
+      <c r="B30" t="s">
         <v>18</v>
       </c>
-      <c r="E28" t="s">
-        <v>83</v>
-      </c>
-      <c r="F28">
-        <v>979.88</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>101</v>
-      </c>
-      <c r="B29" t="s">
-        <v>82</v>
-      </c>
-      <c r="C29" t="s">
-        <v>14</v>
-      </c>
-      <c r="D29" t="s">
-        <v>41</v>
-      </c>
-      <c r="E29" t="s">
-        <v>102</v>
-      </c>
-      <c r="F29" t="s">
-        <v>103</v>
-      </c>
-      <c r="G29" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>105</v>
-      </c>
-      <c r="B30" t="s">
-        <v>23</v>
-      </c>
       <c r="C30" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D30" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E30">
         <v>8</v>
       </c>
-      <c r="F30" t="s">
-        <v>106</v>
+      <c r="F30" s="3" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>107</v>
+      <c r="A31" s="1">
+        <v>45012</v>
       </c>
       <c r="B31" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C31" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D31" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E31">
         <v>12</v>
       </c>
-      <c r="F31" t="s">
-        <v>108</v>
+      <c r="F31" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="G31">
         <v>19460.14</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>109</v>
+      <c r="A32" s="1">
+        <v>45072</v>
       </c>
       <c r="B32" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C32" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D32" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E32" t="s">
+        <v>48</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G32" t="s">
         <v>74</v>
       </c>
-      <c r="F32" t="s">
-        <v>110</v>
-      </c>
-      <c r="G32" t="s">
-        <v>111</v>
-      </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>112</v>
+      <c r="A33" s="1">
+        <v>45106</v>
       </c>
       <c r="B33" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C33" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D33" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E33">
         <v>18</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="3">
         <v>4896.72</v>
       </c>
       <c r="G33" t="s">
-        <v>113</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>114</v>
+      <c r="A34" s="1">
+        <v>44973</v>
       </c>
       <c r="B34" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C34" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D34" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E34">
         <v>4</v>
       </c>
-      <c r="F34" t="s">
-        <v>115</v>
+      <c r="F34" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="G34">
         <v>50350.3</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>89</v>
+      <c r="A35" s="1">
+        <v>45091</v>
       </c>
       <c r="B35" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="D35" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E35">
         <v>10</v>
       </c>
-      <c r="F35" t="s">
-        <v>116</v>
+      <c r="F35" s="3" t="s">
+        <v>77</v>
       </c>
       <c r="G35">
         <v>14016.9</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>117</v>
+      <c r="A36" s="1">
+        <v>45068</v>
       </c>
       <c r="B36" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D36" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E36" t="s">
-        <v>34</v>
-      </c>
-      <c r="F36" t="s">
-        <v>118</v>
+        <v>24</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="G36">
         <v>7245.21</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>119</v>
+      <c r="A37" s="1">
+        <v>45091</v>
       </c>
       <c r="B37" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="C37" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D37" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E37">
         <v>10</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="3">
         <v>4776.49</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>120</v>
+      <c r="A38" s="1">
+        <v>44954</v>
       </c>
       <c r="B38" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C38" t="s">
-        <v>121</v>
+        <v>79</v>
       </c>
       <c r="D38" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E38" t="s">
-        <v>38</v>
-      </c>
-      <c r="F38" t="s">
-        <v>122</v>
+        <v>26</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="G38" t="s">
-        <v>123</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>124</v>
+      <c r="A39" s="1">
+        <v>45020</v>
       </c>
       <c r="B39" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="C39" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D39" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E39">
         <v>13</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="3">
         <v>423.3</v>
       </c>
       <c r="G39" t="s">
-        <v>125</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>126</v>
+      <c r="A40" s="1">
+        <v>45218</v>
       </c>
       <c r="B40" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" t="s">
+        <v>30</v>
+      </c>
+      <c r="D40" t="s">
         <v>13</v>
-      </c>
-      <c r="C40" t="s">
-        <v>45</v>
-      </c>
-      <c r="D40" t="s">
-        <v>15</v>
       </c>
       <c r="E40">
         <v>6</v>
       </c>
-      <c r="F40" t="s">
-        <v>127</v>
+      <c r="F40" s="3" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>128</v>
+      <c r="A41" s="1">
+        <v>45226</v>
       </c>
       <c r="B41" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C41" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="D41" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E41">
         <v>14</v>
       </c>
-      <c r="F41" t="s">
-        <v>129</v>
+      <c r="F41" s="3" t="s">
+        <v>84</v>
       </c>
       <c r="G41" t="s">
-        <v>130</v>
+        <v>85</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>131</v>
+      <c r="A42" s="1">
+        <v>45152</v>
       </c>
       <c r="B42" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C42" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D42" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E42">
         <v>11</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="3">
         <v>1649.02</v>
       </c>
       <c r="G42">
@@ -2173,197 +1856,197 @@
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>132</v>
+      <c r="A43" s="1">
+        <v>45069</v>
       </c>
       <c r="B43" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C43" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D43" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E43">
         <v>13</v>
       </c>
-      <c r="F43" t="s">
-        <v>133</v>
+      <c r="F43" s="3" t="s">
+        <v>86</v>
       </c>
       <c r="G43">
         <v>40814.730000000003</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>134</v>
+      <c r="A44" s="1">
+        <v>45027</v>
       </c>
       <c r="B44" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C44" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D44" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E44" t="s">
-        <v>50</v>
-      </c>
-      <c r="F44" t="s">
-        <v>135</v>
+        <v>33</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>136</v>
+      <c r="A45" s="1">
+        <v>44999</v>
       </c>
       <c r="B45" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C45" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D45" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E45">
         <v>17</v>
       </c>
-      <c r="F45">
+      <c r="F45" s="3">
         <v>4697.54</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>137</v>
+      <c r="A46" s="1">
+        <v>45132</v>
       </c>
       <c r="B46" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C46" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D46" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E46">
         <v>7</v>
       </c>
-      <c r="F46" t="s">
-        <v>138</v>
+      <c r="F46" s="3" t="s">
+        <v>88</v>
       </c>
       <c r="G46" t="s">
-        <v>139</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>140</v>
+      <c r="A47" s="1">
+        <v>45219</v>
       </c>
       <c r="B47" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="C47" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="D47" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E47">
         <v>2</v>
       </c>
-      <c r="F47" t="s">
-        <v>141</v>
+      <c r="F47" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="G47">
         <v>1650.69</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>142</v>
+      <c r="A48" s="1">
+        <v>45273</v>
       </c>
       <c r="B48" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C48" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="D48" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E48">
         <v>16</v>
       </c>
-      <c r="F48" t="s">
-        <v>143</v>
+      <c r="F48" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="G48">
         <v>5367.48</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>144</v>
+      <c r="A49" s="1">
+        <v>45140</v>
       </c>
       <c r="B49" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C49" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D49" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E49">
         <v>18</v>
       </c>
-      <c r="F49" t="s">
-        <v>145</v>
+      <c r="F49" s="3" t="s">
+        <v>92</v>
       </c>
       <c r="G49">
         <v>94270.399999999994</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>146</v>
+      <c r="A50" s="1">
+        <v>45207</v>
       </c>
       <c r="B50" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C50" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="D50" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E50">
         <v>16</v>
       </c>
-      <c r="F50" t="s">
-        <v>147</v>
+      <c r="F50" s="3" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>148</v>
+      <c r="A51" s="1">
+        <v>44975</v>
       </c>
       <c r="B51" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C51" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="D51" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E51">
         <v>10</v>
       </c>
-      <c r="F51">
+      <c r="F51" s="3">
         <v>3936.93</v>
       </c>
       <c r="G51">
@@ -2371,220 +2054,220 @@
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>149</v>
+      <c r="A52" s="1">
+        <v>44977</v>
       </c>
       <c r="B52" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C52" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D52" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E52" t="s">
-        <v>71</v>
-      </c>
-      <c r="F52">
+        <v>46</v>
+      </c>
+      <c r="F52" s="3">
         <v>4087.23</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>150</v>
+      <c r="A53" s="1">
+        <v>45280</v>
       </c>
       <c r="B53" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C53" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D53" t="s">
+        <v>15</v>
+      </c>
+      <c r="E53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>45274</v>
+      </c>
+      <c r="B54" t="s">
         <v>18</v>
       </c>
-      <c r="E53" t="s">
-        <v>42</v>
-      </c>
-      <c r="F53" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>152</v>
-      </c>
-      <c r="B54" t="s">
-        <v>23</v>
-      </c>
       <c r="C54" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="D54" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E54">
         <v>17</v>
       </c>
-      <c r="F54" t="s">
-        <v>153</v>
+      <c r="F54" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="G54">
         <v>2849.38</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>154</v>
+      <c r="A55" s="1">
+        <v>45182</v>
       </c>
       <c r="B55" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C55" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D55" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E55">
         <v>8</v>
       </c>
-      <c r="F55" t="s">
-        <v>155</v>
+      <c r="F55" s="3" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>156</v>
+      <c r="A56" s="1">
+        <v>45194</v>
       </c>
       <c r="B56" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C56" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D56" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E56" t="s">
-        <v>50</v>
-      </c>
-      <c r="F56" t="s">
-        <v>157</v>
+        <v>33</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="G56">
         <v>1355.25</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>158</v>
+      <c r="A57" s="1">
+        <v>45271</v>
       </c>
       <c r="B57" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C57" t="s">
-        <v>121</v>
+        <v>79</v>
       </c>
       <c r="D57" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E57">
         <v>8</v>
       </c>
-      <c r="F57" t="s">
-        <v>159</v>
+      <c r="F57" s="3" t="s">
+        <v>98</v>
       </c>
       <c r="G57">
         <v>35404.199999999997</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>160</v>
+      <c r="A58" s="1">
+        <v>45146</v>
       </c>
       <c r="B58" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="C58" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="D58" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E58">
         <v>16</v>
       </c>
-      <c r="F58">
+      <c r="F58" s="3">
         <v>1211.28</v>
       </c>
       <c r="G58" t="s">
-        <v>161</v>
+        <v>99</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>162</v>
+      <c r="A59" s="1">
+        <v>45264</v>
       </c>
       <c r="B59" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C59" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="D59" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E59">
         <v>12</v>
       </c>
-      <c r="F59">
+      <c r="F59" s="3">
         <v>1417.08</v>
       </c>
       <c r="G59" t="s">
-        <v>163</v>
+        <v>100</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>164</v>
+      <c r="A60" s="1">
+        <v>45161</v>
       </c>
       <c r="B60" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C60" t="s">
-        <v>121</v>
+        <v>79</v>
       </c>
       <c r="D60" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E60">
         <v>16</v>
       </c>
-      <c r="F60" t="s">
-        <v>165</v>
+      <c r="F60" s="3" t="s">
+        <v>101</v>
       </c>
       <c r="G60" t="s">
-        <v>166</v>
+        <v>102</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>167</v>
+      <c r="A61" s="1">
+        <v>45140</v>
       </c>
       <c r="B61" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C61" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D61" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E61" t="s">
-        <v>90</v>
-      </c>
-      <c r="F61">
+        <v>60</v>
+      </c>
+      <c r="F61" s="3">
         <v>775.3</v>
       </c>
       <c r="G61">
@@ -2592,659 +2275,659 @@
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>168</v>
+      <c r="A62" s="1">
+        <v>45169</v>
       </c>
       <c r="B62" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C62" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D62" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E62" t="s">
-        <v>46</v>
-      </c>
-      <c r="F62" t="s">
-        <v>169</v>
+        <v>31</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>103</v>
       </c>
       <c r="G62" t="s">
-        <v>170</v>
+        <v>104</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>171</v>
+      <c r="A63" s="1">
+        <v>45218</v>
       </c>
       <c r="B63" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C63" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D63" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E63" t="s">
-        <v>93</v>
-      </c>
-      <c r="F63">
+        <v>62</v>
+      </c>
+      <c r="F63" s="3">
         <v>2388.29</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>172</v>
+      <c r="A64" s="1">
+        <v>45082</v>
       </c>
       <c r="B64" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C64" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="D64" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E64">
         <v>10</v>
       </c>
-      <c r="F64">
+      <c r="F64" s="3">
         <v>3624.07</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>173</v>
+      <c r="A65" s="1">
+        <v>45155</v>
       </c>
       <c r="B65" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C65" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D65" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E65">
         <v>20</v>
       </c>
-      <c r="F65" t="s">
-        <v>174</v>
+      <c r="F65" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="G65">
         <v>4847.9399999999996</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>175</v>
+      <c r="A66" s="1">
+        <v>45047</v>
       </c>
       <c r="B66" t="s">
+        <v>11</v>
+      </c>
+      <c r="C66" t="s">
+        <v>12</v>
+      </c>
+      <c r="D66" t="s">
         <v>13</v>
-      </c>
-      <c r="C66" t="s">
-        <v>14</v>
-      </c>
-      <c r="D66" t="s">
-        <v>15</v>
       </c>
       <c r="E66">
         <v>7</v>
       </c>
-      <c r="F66" t="s">
-        <v>176</v>
+      <c r="F66" s="3" t="s">
+        <v>106</v>
       </c>
       <c r="G66">
         <v>41961.599999999999</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>177</v>
+      <c r="A67" s="1">
+        <v>45291</v>
       </c>
       <c r="B67" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" t="s">
+        <v>25</v>
+      </c>
+      <c r="D67" t="s">
+        <v>28</v>
+      </c>
+      <c r="E67" t="s">
+        <v>51</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>44959</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="s">
         <v>8</v>
       </c>
-      <c r="C67" t="s">
-        <v>37</v>
-      </c>
-      <c r="D67" t="s">
-        <v>41</v>
-      </c>
-      <c r="E67" t="s">
-        <v>78</v>
-      </c>
-      <c r="F67" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>179</v>
-      </c>
-      <c r="B68" t="s">
-        <v>20</v>
-      </c>
-      <c r="C68" t="s">
-        <v>9</v>
-      </c>
       <c r="D68" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E68" t="s">
-        <v>180</v>
-      </c>
-      <c r="F68" t="s">
-        <v>181</v>
+        <v>108</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>109</v>
       </c>
       <c r="G68">
         <v>42995.7</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>182</v>
+      <c r="A69" s="1">
+        <v>45128</v>
       </c>
       <c r="B69" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="C69" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D69" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E69">
         <v>20</v>
       </c>
-      <c r="F69" t="s">
-        <v>183</v>
+      <c r="F69" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="G69" t="s">
-        <v>184</v>
+        <v>111</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>185</v>
+      <c r="A70" s="1">
+        <v>45187</v>
       </c>
       <c r="B70" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70" t="s">
+        <v>20</v>
+      </c>
+      <c r="D70" t="s">
+        <v>15</v>
+      </c>
+      <c r="E70" t="s">
+        <v>60</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>45196</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="s">
+        <v>17</v>
+      </c>
+      <c r="D71" t="s">
         <v>13</v>
-      </c>
-      <c r="C70" t="s">
-        <v>27</v>
-      </c>
-      <c r="D70" t="s">
-        <v>18</v>
-      </c>
-      <c r="E70" t="s">
-        <v>90</v>
-      </c>
-      <c r="F70" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>187</v>
-      </c>
-      <c r="B71" t="s">
-        <v>20</v>
-      </c>
-      <c r="C71" t="s">
-        <v>21</v>
-      </c>
-      <c r="D71" t="s">
-        <v>15</v>
       </c>
       <c r="E71">
         <v>8</v>
       </c>
-      <c r="F71" t="s">
-        <v>188</v>
+      <c r="F71" s="3" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>189</v>
+      <c r="A72" s="1">
+        <v>45062</v>
       </c>
       <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="s">
         <v>20</v>
       </c>
-      <c r="C72" t="s">
-        <v>27</v>
-      </c>
       <c r="D72" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E72" t="s">
-        <v>83</v>
-      </c>
-      <c r="F72" t="s">
-        <v>190</v>
+        <v>55</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="G72">
         <v>27462.82</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>191</v>
+      <c r="A73" s="1">
+        <v>45286</v>
       </c>
       <c r="B73" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="C73" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D73" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E73">
         <v>1</v>
       </c>
-      <c r="F73" t="s">
-        <v>192</v>
+      <c r="F73" s="3" t="s">
+        <v>115</v>
       </c>
       <c r="G73" t="s">
-        <v>193</v>
+        <v>116</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>194</v>
+      <c r="A74" s="1">
+        <v>45169</v>
       </c>
       <c r="B74" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C74" t="s">
-        <v>121</v>
+        <v>79</v>
       </c>
       <c r="D74" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E74">
         <v>11</v>
       </c>
-      <c r="F74" t="s">
-        <v>195</v>
+      <c r="F74" s="3" t="s">
+        <v>117</v>
       </c>
       <c r="G74" t="s">
-        <v>196</v>
+        <v>118</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>197</v>
+      <c r="A75" s="1">
+        <v>44944</v>
       </c>
       <c r="B75" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C75" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D75" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E75">
         <v>14</v>
       </c>
-      <c r="F75" t="s">
-        <v>198</v>
+      <c r="F75" s="3" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>199</v>
+      <c r="A76" s="1">
+        <v>45211</v>
       </c>
       <c r="B76" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C76" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D76" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E76">
         <v>5</v>
       </c>
-      <c r="F76" t="s">
-        <v>200</v>
+      <c r="F76" s="3" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>201</v>
+      <c r="A77" s="1">
+        <v>45070</v>
       </c>
       <c r="B77" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C77" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D77" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E77">
         <v>9</v>
       </c>
-      <c r="F77" t="s">
-        <v>202</v>
+      <c r="F77" s="3" t="s">
+        <v>121</v>
       </c>
       <c r="G77">
         <v>591.94000000000005</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>203</v>
+      <c r="A78" s="1">
+        <v>45266</v>
       </c>
       <c r="B78" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C78" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D78" t="s">
+        <v>13</v>
+      </c>
+      <c r="E78" t="s">
+        <v>24</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G78" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>45117</v>
+      </c>
+      <c r="B79" t="s">
+        <v>18</v>
+      </c>
+      <c r="C79" t="s">
+        <v>30</v>
+      </c>
+      <c r="D79" t="s">
         <v>15</v>
       </c>
-      <c r="E78" t="s">
-        <v>34</v>
-      </c>
-      <c r="F78" t="s">
-        <v>204</v>
-      </c>
-      <c r="G78" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>206</v>
-      </c>
-      <c r="B79" t="s">
-        <v>23</v>
-      </c>
-      <c r="C79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D79" t="s">
-        <v>18</v>
-      </c>
       <c r="E79" t="s">
-        <v>30</v>
-      </c>
-      <c r="F79">
+        <v>22</v>
+      </c>
+      <c r="F79" s="3">
         <v>2139.87</v>
       </c>
       <c r="G79" t="s">
-        <v>207</v>
+        <v>124</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>208</v>
+      <c r="A80" s="1">
+        <v>45016</v>
       </c>
       <c r="B80" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C80" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D80" t="s">
+        <v>13</v>
+      </c>
+      <c r="E80" t="s">
+        <v>125</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>45086</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="s">
+        <v>14</v>
+      </c>
+      <c r="D81" t="s">
         <v>15</v>
-      </c>
-      <c r="E80" t="s">
-        <v>209</v>
-      </c>
-      <c r="F80" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>211</v>
-      </c>
-      <c r="B81" t="s">
-        <v>20</v>
-      </c>
-      <c r="C81" t="s">
-        <v>17</v>
-      </c>
-      <c r="D81" t="s">
-        <v>18</v>
       </c>
       <c r="E81">
         <v>3</v>
       </c>
-      <c r="F81" t="s">
-        <v>212</v>
+      <c r="F81" s="3" t="s">
+        <v>127</v>
       </c>
       <c r="G81" t="s">
-        <v>213</v>
+        <v>128</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>214</v>
+      <c r="A82" s="1">
+        <v>45251</v>
       </c>
       <c r="B82" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" t="s">
         <v>8</v>
       </c>
-      <c r="C82" t="s">
-        <v>9</v>
-      </c>
       <c r="D82" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E82" t="s">
-        <v>209</v>
-      </c>
-      <c r="F82" t="s">
-        <v>215</v>
+        <v>125</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>216</v>
+      <c r="A83" s="1">
+        <v>45058</v>
       </c>
       <c r="B83" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C83" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="D83" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E83">
         <v>7</v>
       </c>
-      <c r="F83" t="s">
-        <v>217</v>
+      <c r="F83" s="3" t="s">
+        <v>130</v>
       </c>
       <c r="G83">
         <v>63043.9</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>218</v>
+      <c r="A84" s="1">
+        <v>44947</v>
       </c>
       <c r="B84" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C84" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D84" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E84" t="s">
-        <v>74</v>
-      </c>
-      <c r="F84" t="s">
-        <v>219</v>
+        <v>48</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>131</v>
       </c>
       <c r="G84">
         <v>45948.27</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>220</v>
+      <c r="A85" s="1">
+        <v>44980</v>
       </c>
       <c r="B85" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C85" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D85" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E85">
         <v>14</v>
       </c>
-      <c r="F85">
+      <c r="F85" s="3">
         <v>2679.53</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>221</v>
+      <c r="A86" s="1">
+        <v>45040</v>
       </c>
       <c r="B86" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C86" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D86" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E86">
         <v>1</v>
       </c>
-      <c r="F86" t="s">
-        <v>222</v>
+      <c r="F86" s="3" t="s">
+        <v>132</v>
       </c>
       <c r="G86" t="s">
-        <v>223</v>
+        <v>133</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>224</v>
+      <c r="A87" s="1">
+        <v>45182</v>
       </c>
       <c r="B87" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C87" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="D87" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E87" t="s">
-        <v>54</v>
-      </c>
-      <c r="F87" t="s">
-        <v>225</v>
+        <v>35</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="G87">
         <v>1559.04</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>226</v>
+      <c r="A88" s="1">
+        <v>44981</v>
       </c>
       <c r="B88" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C88" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="D88" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E88" t="s">
-        <v>46</v>
-      </c>
-      <c r="F88" t="s">
-        <v>227</v>
+        <v>31</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>135</v>
       </c>
       <c r="G88">
         <v>2472.09</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>228</v>
+      <c r="A89" s="1">
+        <v>45213</v>
       </c>
       <c r="B89" t="s">
+        <v>11</v>
+      </c>
+      <c r="C89" t="s">
+        <v>30</v>
+      </c>
+      <c r="D89" t="s">
         <v>13</v>
       </c>
-      <c r="C89" t="s">
+      <c r="E89" t="s">
+        <v>35</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G89" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
+        <v>45133</v>
+      </c>
+      <c r="B90" t="s">
+        <v>54</v>
+      </c>
+      <c r="C90" t="s">
         <v>45</v>
       </c>
-      <c r="D89" t="s">
+      <c r="D90" t="s">
         <v>15</v>
-      </c>
-      <c r="E89" t="s">
-        <v>54</v>
-      </c>
-      <c r="F89" t="s">
-        <v>229</v>
-      </c>
-      <c r="G89" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>231</v>
-      </c>
-      <c r="B90" t="s">
-        <v>82</v>
-      </c>
-      <c r="C90" t="s">
-        <v>70</v>
-      </c>
-      <c r="D90" t="s">
-        <v>18</v>
       </c>
       <c r="E90">
         <v>3</v>
       </c>
-      <c r="F90" t="s">
-        <v>232</v>
+      <c r="F90" s="3" t="s">
+        <v>138</v>
       </c>
       <c r="G90" t="s">
-        <v>233</v>
+        <v>139</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>234</v>
+      <c r="A91" s="1">
+        <v>45133</v>
       </c>
       <c r="B91" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C91" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D91" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E91" t="s">
-        <v>34</v>
-      </c>
-      <c r="F91">
+        <v>24</v>
+      </c>
+      <c r="F91" s="3">
         <v>3418.73</v>
       </c>
       <c r="G91">
@@ -3252,332 +2935,332 @@
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>235</v>
+      <c r="A92" s="1">
+        <v>45029</v>
       </c>
       <c r="B92" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C92" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D92" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E92" t="s">
-        <v>83</v>
-      </c>
-      <c r="F92" t="s">
-        <v>236</v>
+        <v>55</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>140</v>
       </c>
       <c r="G92" t="s">
-        <v>237</v>
+        <v>141</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>44</v>
+      <c r="A93" s="1">
+        <v>45261</v>
       </c>
       <c r="B93" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C93" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D93" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E93">
         <v>5</v>
       </c>
-      <c r="F93" t="s">
-        <v>238</v>
+      <c r="F93" s="3" t="s">
+        <v>142</v>
       </c>
       <c r="G93" t="s">
-        <v>239</v>
+        <v>143</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>240</v>
+      <c r="A94" s="1">
+        <v>45248</v>
       </c>
       <c r="B94" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C94" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D94" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E94" t="s">
-        <v>180</v>
-      </c>
-      <c r="F94" t="s">
-        <v>241</v>
+        <v>108</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>144</v>
       </c>
       <c r="G94">
         <v>23119.88</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>242</v>
+      <c r="A95" s="1">
+        <v>45093</v>
       </c>
       <c r="B95" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C95" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="D95" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E95">
         <v>20</v>
       </c>
-      <c r="F95" t="s">
-        <v>243</v>
+      <c r="F95" s="3" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>244</v>
+      <c r="A96" s="1">
+        <v>45081</v>
       </c>
       <c r="B96" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C96" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D96" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E96" t="s">
-        <v>50</v>
-      </c>
-      <c r="F96" t="s">
-        <v>245</v>
+        <v>33</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>146</v>
       </c>
       <c r="G96">
         <v>31034.99</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>246</v>
+      <c r="A97" s="1">
+        <v>44959</v>
       </c>
       <c r="B97" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="C97" t="s">
-        <v>121</v>
+        <v>79</v>
       </c>
       <c r="D97" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E97">
         <v>2</v>
       </c>
-      <c r="F97">
+      <c r="F97" s="3">
         <v>1034.1099999999999</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>247</v>
+      <c r="A98" s="1">
+        <v>45097</v>
       </c>
       <c r="B98" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="C98" t="s">
+        <v>21</v>
+      </c>
+      <c r="D98" t="s">
+        <v>28</v>
+      </c>
+      <c r="E98" t="s">
         <v>29</v>
       </c>
-      <c r="D98" t="s">
-        <v>41</v>
-      </c>
-      <c r="E98" t="s">
-        <v>42</v>
-      </c>
-      <c r="F98" t="s">
-        <v>248</v>
+      <c r="F98" s="3" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>249</v>
+      <c r="A99" s="1">
+        <v>45012</v>
       </c>
       <c r="B99" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="C99" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D99" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E99" t="s">
-        <v>250</v>
-      </c>
-      <c r="F99">
+        <v>148</v>
+      </c>
+      <c r="F99" s="3">
         <v>3109.51</v>
       </c>
       <c r="G99" t="s">
-        <v>251</v>
+        <v>149</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>252</v>
+      <c r="A100" s="1">
+        <v>45253</v>
       </c>
       <c r="B100" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C100" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D100" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E100">
         <v>4</v>
       </c>
-      <c r="F100">
+      <c r="F100" s="3">
         <v>1570.38</v>
       </c>
       <c r="G100" t="s">
-        <v>253</v>
+        <v>150</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>254</v>
+      <c r="A101" s="1">
+        <v>45175</v>
       </c>
       <c r="B101" t="s">
+        <v>11</v>
+      </c>
+      <c r="C101" t="s">
+        <v>25</v>
+      </c>
+      <c r="D101" t="s">
         <v>13</v>
       </c>
-      <c r="C101" t="s">
-        <v>37</v>
-      </c>
-      <c r="D101" t="s">
-        <v>15</v>
-      </c>
       <c r="E101" t="s">
-        <v>250</v>
-      </c>
-      <c r="F101" t="s">
-        <v>255</v>
+        <v>148</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>151</v>
       </c>
       <c r="G101" t="s">
-        <v>256</v>
+        <v>152</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>257</v>
+      <c r="A102" s="1">
+        <v>45268</v>
       </c>
       <c r="B102" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C102" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D102" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E102" t="s">
-        <v>67</v>
-      </c>
-      <c r="F102" t="s">
-        <v>258</v>
+        <v>43</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>153</v>
       </c>
       <c r="G102">
         <v>19227.509999999998</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>203</v>
+      <c r="A103" s="1">
+        <v>45266</v>
       </c>
       <c r="B103" t="s">
+        <v>11</v>
+      </c>
+      <c r="C103" t="s">
+        <v>65</v>
+      </c>
+      <c r="D103" t="s">
         <v>13</v>
-      </c>
-      <c r="C103" t="s">
-        <v>97</v>
-      </c>
-      <c r="D103" t="s">
-        <v>15</v>
       </c>
       <c r="E103">
         <v>15</v>
       </c>
-      <c r="F103">
+      <c r="F103" s="3">
         <v>1886.49</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>259</v>
+      <c r="A104" s="1">
+        <v>45145</v>
       </c>
       <c r="B104" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C104" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D104" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E104">
         <v>3</v>
       </c>
-      <c r="F104" t="s">
-        <v>260</v>
+      <c r="F104" s="3" t="s">
+        <v>154</v>
       </c>
       <c r="G104" t="s">
-        <v>261</v>
+        <v>155</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>262</v>
+      <c r="A105" s="1">
+        <v>45250</v>
       </c>
       <c r="B105" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C105" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D105" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E105">
         <v>2</v>
       </c>
-      <c r="F105" t="s">
-        <v>263</v>
+      <c r="F105" s="3" t="s">
+        <v>156</v>
       </c>
       <c r="G105" t="s">
-        <v>264</v>
+        <v>157</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>265</v>
+      <c r="A106" s="1">
+        <v>45173</v>
       </c>
       <c r="B106" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C106" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D106" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E106" t="s">
-        <v>54</v>
-      </c>
-      <c r="F106">
+        <v>35</v>
+      </c>
+      <c r="F106" s="3">
         <v>3110.71</v>
       </c>
       <c r="G106">
@@ -3585,65 +3268,65 @@
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>266</v>
+      <c r="A107" s="1">
+        <v>45234</v>
       </c>
       <c r="B107" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C107" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D107" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E107">
         <v>17</v>
       </c>
-      <c r="F107" t="s">
-        <v>267</v>
+      <c r="F107" s="3" t="s">
+        <v>158</v>
       </c>
       <c r="G107" t="s">
-        <v>268</v>
+        <v>159</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>269</v>
+      <c r="A108" s="1">
+        <v>45144</v>
       </c>
       <c r="B108" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="C108" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D108" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E108">
         <v>17</v>
       </c>
-      <c r="F108" t="s">
-        <v>270</v>
+      <c r="F108" s="3" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>271</v>
+      <c r="A109" s="1">
+        <v>45228</v>
       </c>
       <c r="B109" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C109" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="D109" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E109" t="s">
-        <v>67</v>
-      </c>
-      <c r="F109">
+        <v>43</v>
+      </c>
+      <c r="F109" s="3">
         <v>1108.71</v>
       </c>
       <c r="G109">
@@ -3651,22 +3334,22 @@
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>272</v>
+      <c r="A110" s="1">
+        <v>45284</v>
       </c>
       <c r="B110" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C110" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D110" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E110" t="s">
-        <v>54</v>
-      </c>
-      <c r="F110">
+        <v>35</v>
+      </c>
+      <c r="F110" s="3">
         <v>670.54</v>
       </c>
       <c r="G110">
@@ -3674,22 +3357,22 @@
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>273</v>
+      <c r="A111" s="1">
+        <v>45250</v>
       </c>
       <c r="B111" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="C111" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D111" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E111" t="s">
-        <v>30</v>
-      </c>
-      <c r="F111">
+        <v>22</v>
+      </c>
+      <c r="F111" s="3">
         <v>702.91</v>
       </c>
       <c r="G111">
@@ -3697,233 +3380,235 @@
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>274</v>
+      <c r="A112" s="1">
+        <v>44983</v>
       </c>
       <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="s">
         <v>20</v>
       </c>
-      <c r="C112" t="s">
-        <v>27</v>
-      </c>
       <c r="D112" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E112" t="s">
-        <v>83</v>
-      </c>
-      <c r="F112" t="s">
-        <v>275</v>
+        <v>55</v>
+      </c>
+      <c r="F112" s="3">
+        <v>1348.91</v>
       </c>
       <c r="G112">
         <v>25629.29</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>276</v>
+      <c r="A113" s="1">
+        <v>45263</v>
       </c>
       <c r="B113" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C113" t="s">
+        <v>8</v>
+      </c>
+      <c r="D113" t="s">
+        <v>13</v>
+      </c>
+      <c r="E113" t="s">
+        <v>31</v>
+      </c>
+      <c r="F113" s="3">
+        <v>3218.22</v>
+      </c>
+      <c r="G113" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
+        <v>44990</v>
+      </c>
+      <c r="B114" t="s">
+        <v>54</v>
+      </c>
+      <c r="C114" t="s">
+        <v>65</v>
+      </c>
+      <c r="D114" t="s">
+        <v>19</v>
+      </c>
+      <c r="E114" t="s">
+        <v>29</v>
+      </c>
+      <c r="F114" s="3">
+        <v>303.69</v>
+      </c>
+      <c r="G114" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
+        <v>45207</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="s">
+        <v>32</v>
+      </c>
+      <c r="D115" t="s">
+        <v>15</v>
+      </c>
+      <c r="E115" t="s">
+        <v>55</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G115" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
+        <v>44986</v>
+      </c>
+      <c r="B116" t="s">
+        <v>54</v>
+      </c>
+      <c r="C116" t="s">
+        <v>79</v>
+      </c>
+      <c r="D116" t="s">
         <v>9</v>
       </c>
-      <c r="D113" t="s">
-        <v>15</v>
-      </c>
-      <c r="E113" t="s">
-        <v>46</v>
-      </c>
-      <c r="F113">
-        <v>3218.22</v>
-      </c>
-      <c r="G113" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>278</v>
-      </c>
-      <c r="B114" t="s">
-        <v>82</v>
-      </c>
-      <c r="C114" t="s">
-        <v>97</v>
-      </c>
-      <c r="D114" t="s">
-        <v>24</v>
-      </c>
-      <c r="E114" t="s">
-        <v>42</v>
-      </c>
-      <c r="F114">
-        <v>303.69</v>
-      </c>
-      <c r="G114" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>280</v>
-      </c>
-      <c r="B115" t="s">
-        <v>20</v>
-      </c>
-      <c r="C115" t="s">
-        <v>49</v>
-      </c>
-      <c r="D115" t="s">
-        <v>18</v>
-      </c>
-      <c r="E115" t="s">
-        <v>83</v>
-      </c>
-      <c r="F115" t="s">
-        <v>281</v>
-      </c>
-      <c r="G115" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>283</v>
-      </c>
-      <c r="B116" t="s">
-        <v>82</v>
-      </c>
-      <c r="C116" t="s">
-        <v>121</v>
-      </c>
-      <c r="D116" t="s">
-        <v>10</v>
-      </c>
       <c r="E116" t="s">
-        <v>90</v>
-      </c>
-      <c r="F116" t="s">
-        <v>284</v>
+        <v>60</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>165</v>
       </c>
       <c r="G116" t="s">
-        <v>285</v>
+        <v>166</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>286</v>
+      <c r="A117" s="1">
+        <v>44932</v>
       </c>
       <c r="B117" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C117" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="D117" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E117">
         <v>20</v>
       </c>
-      <c r="F117" t="s">
-        <v>287</v>
+      <c r="F117" s="3" t="s">
+        <v>167</v>
       </c>
       <c r="G117" t="s">
-        <v>288</v>
+        <v>168</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>289</v>
+      <c r="A118" s="1">
+        <v>45073</v>
       </c>
       <c r="B118" t="s">
+        <v>7</v>
+      </c>
+      <c r="C118" t="s">
         <v>8</v>
       </c>
-      <c r="C118" t="s">
-        <v>9</v>
-      </c>
       <c r="D118" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E118" t="s">
-        <v>290</v>
-      </c>
-      <c r="F118" t="s">
-        <v>291</v>
+        <v>169</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="G118">
         <v>71090.8</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>63</v>
+      <c r="A119" s="1">
+        <v>45188</v>
       </c>
       <c r="B119" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C119" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="D119" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E119" t="s">
-        <v>42</v>
-      </c>
-      <c r="F119" t="s">
-        <v>292</v>
+        <v>29</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>293</v>
+      <c r="A120" s="1">
+        <v>45080</v>
       </c>
       <c r="B120" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C120" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D120" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E120" t="s">
-        <v>46</v>
-      </c>
-      <c r="F120">
+        <v>31</v>
+      </c>
+      <c r="F120" s="3">
         <v>2049.16</v>
       </c>
       <c r="G120" t="s">
-        <v>294</v>
+        <v>172</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>295</v>
+      <c r="A121" s="1">
+        <v>45154</v>
       </c>
       <c r="B121" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C121" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="D121" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E121" t="s">
-        <v>93</v>
-      </c>
-      <c r="F121">
+        <v>62</v>
+      </c>
+      <c r="F121" s="3">
         <v>4390.2700000000004</v>
       </c>
       <c r="G121" t="s">
-        <v>296</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G121" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/dados_tratados.xlsx
+++ b/data/dados_tratados.xlsx
@@ -2,23 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
-  <workbookPr/>
+  <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaike\OneDrive\Documentos\GitHub\analise-vendas-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED63D0E9-93B7-4841-BED5-8E5E22007A6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{248DAA35-834A-496F-92BF-356043426EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Tratados" sheetId="1" r:id="rId1"/>
+    <sheet name="Análises" sheetId="2" r:id="rId2"/>
+    <sheet name="Dashboard" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dados Tratados'!$A$1:$G$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dados Tratados'!$A$2:$G$123</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="12" r:id="rId4"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="45">
   <si>
     <t>Data</t>
   </si>
@@ -107,7 +112,73 @@
     <t>Nordeste</t>
   </si>
   <si>
-    <t>Total</t>
+    <t>Qualitativa Ordinal</t>
+  </si>
+  <si>
+    <t>Qualitativa Nominal</t>
+  </si>
+  <si>
+    <t>Quantitativa Discreta</t>
+  </si>
+  <si>
+    <t>Quantitativa Contínua</t>
+  </si>
+  <si>
+    <t>Total Geral</t>
+  </si>
+  <si>
+    <t>Soma de Receita</t>
+  </si>
+  <si>
+    <t>jan</t>
+  </si>
+  <si>
+    <t>fev</t>
+  </si>
+  <si>
+    <t>mar</t>
+  </si>
+  <si>
+    <t>abr</t>
+  </si>
+  <si>
+    <t>mai</t>
+  </si>
+  <si>
+    <t>jun</t>
+  </si>
+  <si>
+    <t>jul</t>
+  </si>
+  <si>
+    <t>ago</t>
+  </si>
+  <si>
+    <t>set</t>
+  </si>
+  <si>
+    <t>out</t>
+  </si>
+  <si>
+    <t>nov</t>
+  </si>
+  <si>
+    <t>dez</t>
+  </si>
+  <si>
+    <t>Faturamento</t>
+  </si>
+  <si>
+    <t>Quantidade Total de Vendas</t>
+  </si>
+  <si>
+    <t>Ticket Médio</t>
+  </si>
+  <si>
+    <t>Período em Meses</t>
+  </si>
+  <si>
+    <t>Evolução do Faturamento Mensal</t>
   </si>
 </sst>
 </file>
@@ -160,7 +231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -175,11 +246,151 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="27">
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -190,6 +401,3470 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[dados_tratados.xlsx]Análises!Tabela dinâmica3</c:name>
+    <c:fmtId val="1"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Evolução do Faturamento</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Mensal em 2023</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Análises!$C$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Análises!$B$9:$B$21</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>fev</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>mar</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>abr</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>mai</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>jun</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>jul</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>ago</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>set</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>out</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>nov</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>dez</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Análises!$C$9:$C$21</c:f>
+              <c:numCache>
+                <c:formatCode>"R$"\ #,##0.00</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>199573.19000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>169251.27</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>163357.34999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>90114.66</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>160544.88999999998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>232438.85</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>207404.83999999997</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>380675.46000000008</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>226648.61999999997</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>203737.89</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>80338.960000000006</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>227617.42999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-533E-42F1-8882-BBA3ED65D8BC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1395569663"/>
+        <c:axId val="1395571583"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1395569663"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1395571583"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1395571583"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="&quot;R$&quot;\ #,##0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1395569663"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1333500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5961055" cy="561949"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="CaixaDeTexto 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DBD9E55-50C6-46FD-B78B-E40DC7E6EF20}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1333500" y="104775"/>
+          <a:ext cx="5961055" cy="561949"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="3000" b="1"/>
+            <a:t>Análise Exploratória de Dados (EDA)</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Gráfico 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5743C49-45B4-A0A6-ECB9-17A95C2F7616}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Kaike Mendes" refreshedDate="46140.468521990741" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="120" xr:uid="{8187D5FB-0263-4B3A-9165-3C5B41DB815C}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A2:G122" sheet="Dados Tratados"/>
+  </cacheSource>
+  <cacheFields count="9">
+    <cacheField name="Data" numFmtId="14">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2023-01-06T00:00:00" maxDate="2024-01-01T00:00:00" count="105">
+        <d v="2023-01-06T00:00:00"/>
+        <d v="2023-01-07T00:00:00"/>
+        <d v="2023-01-11T00:00:00"/>
+        <d v="2023-01-12T00:00:00"/>
+        <d v="2023-01-17T00:00:00"/>
+        <d v="2023-01-18T00:00:00"/>
+        <d v="2023-01-21T00:00:00"/>
+        <d v="2023-01-28T00:00:00"/>
+        <d v="2023-02-02T00:00:00"/>
+        <d v="2023-02-09T00:00:00"/>
+        <d v="2023-02-10T00:00:00"/>
+        <d v="2023-02-14T00:00:00"/>
+        <d v="2023-02-16T00:00:00"/>
+        <d v="2023-02-18T00:00:00"/>
+        <d v="2023-02-20T00:00:00"/>
+        <d v="2023-02-22T00:00:00"/>
+        <d v="2023-02-23T00:00:00"/>
+        <d v="2023-02-24T00:00:00"/>
+        <d v="2023-02-26T00:00:00"/>
+        <d v="2023-03-01T00:00:00"/>
+        <d v="2023-03-05T00:00:00"/>
+        <d v="2023-03-12T00:00:00"/>
+        <d v="2023-03-14T00:00:00"/>
+        <d v="2023-03-27T00:00:00"/>
+        <d v="2023-03-31T00:00:00"/>
+        <d v="2023-04-04T00:00:00"/>
+        <d v="2023-04-11T00:00:00"/>
+        <d v="2023-04-13T00:00:00"/>
+        <d v="2023-04-20T00:00:00"/>
+        <d v="2023-04-21T00:00:00"/>
+        <d v="2023-04-24T00:00:00"/>
+        <d v="2023-04-25T00:00:00"/>
+        <d v="2023-05-01T00:00:00"/>
+        <d v="2023-05-12T00:00:00"/>
+        <d v="2023-05-16T00:00:00"/>
+        <d v="2023-05-19T00:00:00"/>
+        <d v="2023-05-22T00:00:00"/>
+        <d v="2023-05-23T00:00:00"/>
+        <d v="2023-05-24T00:00:00"/>
+        <d v="2023-05-26T00:00:00"/>
+        <d v="2023-05-27T00:00:00"/>
+        <d v="2023-06-03T00:00:00"/>
+        <d v="2023-06-04T00:00:00"/>
+        <d v="2023-06-05T00:00:00"/>
+        <d v="2023-06-09T00:00:00"/>
+        <d v="2023-06-14T00:00:00"/>
+        <d v="2023-06-16T00:00:00"/>
+        <d v="2023-06-20T00:00:00"/>
+        <d v="2023-06-24T00:00:00"/>
+        <d v="2023-06-29T00:00:00"/>
+        <d v="2023-07-04T00:00:00"/>
+        <d v="2023-07-07T00:00:00"/>
+        <d v="2023-07-10T00:00:00"/>
+        <d v="2023-07-14T00:00:00"/>
+        <d v="2023-07-21T00:00:00"/>
+        <d v="2023-07-24T00:00:00"/>
+        <d v="2023-07-25T00:00:00"/>
+        <d v="2023-07-26T00:00:00"/>
+        <d v="2023-08-02T00:00:00"/>
+        <d v="2023-08-03T00:00:00"/>
+        <d v="2023-08-06T00:00:00"/>
+        <d v="2023-08-07T00:00:00"/>
+        <d v="2023-08-08T00:00:00"/>
+        <d v="2023-08-14T00:00:00"/>
+        <d v="2023-08-16T00:00:00"/>
+        <d v="2023-08-17T00:00:00"/>
+        <d v="2023-08-23T00:00:00"/>
+        <d v="2023-08-31T00:00:00"/>
+        <d v="2023-09-04T00:00:00"/>
+        <d v="2023-09-06T00:00:00"/>
+        <d v="2023-09-08T00:00:00"/>
+        <d v="2023-09-13T00:00:00"/>
+        <d v="2023-09-18T00:00:00"/>
+        <d v="2023-09-19T00:00:00"/>
+        <d v="2023-09-25T00:00:00"/>
+        <d v="2023-09-26T00:00:00"/>
+        <d v="2023-09-27T00:00:00"/>
+        <d v="2023-10-06T00:00:00"/>
+        <d v="2023-10-08T00:00:00"/>
+        <d v="2023-10-12T00:00:00"/>
+        <d v="2023-10-14T00:00:00"/>
+        <d v="2023-10-19T00:00:00"/>
+        <d v="2023-10-20T00:00:00"/>
+        <d v="2023-10-26T00:00:00"/>
+        <d v="2023-10-27T00:00:00"/>
+        <d v="2023-10-29T00:00:00"/>
+        <d v="2023-11-04T00:00:00"/>
+        <d v="2023-11-18T00:00:00"/>
+        <d v="2023-11-20T00:00:00"/>
+        <d v="2023-11-21T00:00:00"/>
+        <d v="2023-11-23T00:00:00"/>
+        <d v="2023-12-01T00:00:00"/>
+        <d v="2023-12-03T00:00:00"/>
+        <d v="2023-12-04T00:00:00"/>
+        <d v="2023-12-06T00:00:00"/>
+        <d v="2023-12-08T00:00:00"/>
+        <d v="2023-12-11T00:00:00"/>
+        <d v="2023-12-13T00:00:00"/>
+        <d v="2023-12-14T00:00:00"/>
+        <d v="2023-12-16T00:00:00"/>
+        <d v="2023-12-20T00:00:00"/>
+        <d v="2023-12-24T00:00:00"/>
+        <d v="2023-12-26T00:00:00"/>
+        <d v="2023-12-28T00:00:00"/>
+        <d v="2023-12-31T00:00:00"/>
+      </sharedItems>
+      <fieldGroup par="8"/>
+    </cacheField>
+    <cacheField name="Produto" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Região" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Vendedor" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Quantidade" numFmtId="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="20"/>
+    </cacheField>
+    <cacheField name="Preço Unitário" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="90.35" maxValue="4961.6000000000004"/>
+    </cacheField>
+    <cacheField name="Receita" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="180.7" maxValue="74634.590000000011"/>
+    </cacheField>
+    <cacheField name="Dias (Data)" numFmtId="0" databaseField="0">
+      <fieldGroup base="0">
+        <rangePr groupBy="days" startDate="2023-01-06T00:00:00" endDate="2024-01-01T00:00:00"/>
+        <groupItems count="368">
+          <s v="&lt;06/01/2023"/>
+          <s v="01/jan"/>
+          <s v="02/jan"/>
+          <s v="03/jan"/>
+          <s v="04/jan"/>
+          <s v="05/jan"/>
+          <s v="06/jan"/>
+          <s v="07/jan"/>
+          <s v="08/jan"/>
+          <s v="09/jan"/>
+          <s v="10/jan"/>
+          <s v="11/jan"/>
+          <s v="12/jan"/>
+          <s v="13/jan"/>
+          <s v="14/jan"/>
+          <s v="15/jan"/>
+          <s v="16/jan"/>
+          <s v="17/jan"/>
+          <s v="18/jan"/>
+          <s v="19/jan"/>
+          <s v="20/jan"/>
+          <s v="21/jan"/>
+          <s v="22/jan"/>
+          <s v="23/jan"/>
+          <s v="24/jan"/>
+          <s v="25/jan"/>
+          <s v="26/jan"/>
+          <s v="27/jan"/>
+          <s v="28/jan"/>
+          <s v="29/jan"/>
+          <s v="30/jan"/>
+          <s v="31/jan"/>
+          <s v="01/fev"/>
+          <s v="02/fev"/>
+          <s v="03/fev"/>
+          <s v="04/fev"/>
+          <s v="05/fev"/>
+          <s v="06/fev"/>
+          <s v="07/fev"/>
+          <s v="08/fev"/>
+          <s v="09/fev"/>
+          <s v="10/fev"/>
+          <s v="11/fev"/>
+          <s v="12/fev"/>
+          <s v="13/fev"/>
+          <s v="14/fev"/>
+          <s v="15/fev"/>
+          <s v="16/fev"/>
+          <s v="17/fev"/>
+          <s v="18/fev"/>
+          <s v="19/fev"/>
+          <s v="20/fev"/>
+          <s v="21/fev"/>
+          <s v="22/fev"/>
+          <s v="23/fev"/>
+          <s v="24/fev"/>
+          <s v="25/fev"/>
+          <s v="26/fev"/>
+          <s v="27/fev"/>
+          <s v="28/fev"/>
+          <s v="29/fev"/>
+          <s v="01/mar"/>
+          <s v="02/mar"/>
+          <s v="03/mar"/>
+          <s v="04/mar"/>
+          <s v="05/mar"/>
+          <s v="06/mar"/>
+          <s v="07/mar"/>
+          <s v="08/mar"/>
+          <s v="09/mar"/>
+          <s v="10/mar"/>
+          <s v="11/mar"/>
+          <s v="12/mar"/>
+          <s v="13/mar"/>
+          <s v="14/mar"/>
+          <s v="15/mar"/>
+          <s v="16/mar"/>
+          <s v="17/mar"/>
+          <s v="18/mar"/>
+          <s v="19/mar"/>
+          <s v="20/mar"/>
+          <s v="21/mar"/>
+          <s v="22/mar"/>
+          <s v="23/mar"/>
+          <s v="24/mar"/>
+          <s v="25/mar"/>
+          <s v="26/mar"/>
+          <s v="27/mar"/>
+          <s v="28/mar"/>
+          <s v="29/mar"/>
+          <s v="30/mar"/>
+          <s v="31/mar"/>
+          <s v="01/abr"/>
+          <s v="02/abr"/>
+          <s v="03/abr"/>
+          <s v="04/abr"/>
+          <s v="05/abr"/>
+          <s v="06/abr"/>
+          <s v="07/abr"/>
+          <s v="08/abr"/>
+          <s v="09/abr"/>
+          <s v="10/abr"/>
+          <s v="11/abr"/>
+          <s v="12/abr"/>
+          <s v="13/abr"/>
+          <s v="14/abr"/>
+          <s v="15/abr"/>
+          <s v="16/abr"/>
+          <s v="17/abr"/>
+          <s v="18/abr"/>
+          <s v="19/abr"/>
+          <s v="20/abr"/>
+          <s v="21/abr"/>
+          <s v="22/abr"/>
+          <s v="23/abr"/>
+          <s v="24/abr"/>
+          <s v="25/abr"/>
+          <s v="26/abr"/>
+          <s v="27/abr"/>
+          <s v="28/abr"/>
+          <s v="29/abr"/>
+          <s v="30/abr"/>
+          <s v="01/mai"/>
+          <s v="02/mai"/>
+          <s v="03/mai"/>
+          <s v="04/mai"/>
+          <s v="05/mai"/>
+          <s v="06/mai"/>
+          <s v="07/mai"/>
+          <s v="08/mai"/>
+          <s v="09/mai"/>
+          <s v="10/mai"/>
+          <s v="11/mai"/>
+          <s v="12/mai"/>
+          <s v="13/mai"/>
+          <s v="14/mai"/>
+          <s v="15/mai"/>
+          <s v="16/mai"/>
+          <s v="17/mai"/>
+          <s v="18/mai"/>
+          <s v="19/mai"/>
+          <s v="20/mai"/>
+          <s v="21/mai"/>
+          <s v="22/mai"/>
+          <s v="23/mai"/>
+          <s v="24/mai"/>
+          <s v="25/mai"/>
+          <s v="26/mai"/>
+          <s v="27/mai"/>
+          <s v="28/mai"/>
+          <s v="29/mai"/>
+          <s v="30/mai"/>
+          <s v="31/mai"/>
+          <s v="01/jun"/>
+          <s v="02/jun"/>
+          <s v="03/jun"/>
+          <s v="04/jun"/>
+          <s v="05/jun"/>
+          <s v="06/jun"/>
+          <s v="07/jun"/>
+          <s v="08/jun"/>
+          <s v="09/jun"/>
+          <s v="10/jun"/>
+          <s v="11/jun"/>
+          <s v="12/jun"/>
+          <s v="13/jun"/>
+          <s v="14/jun"/>
+          <s v="15/jun"/>
+          <s v="16/jun"/>
+          <s v="17/jun"/>
+          <s v="18/jun"/>
+          <s v="19/jun"/>
+          <s v="20/jun"/>
+          <s v="21/jun"/>
+          <s v="22/jun"/>
+          <s v="23/jun"/>
+          <s v="24/jun"/>
+          <s v="25/jun"/>
+          <s v="26/jun"/>
+          <s v="27/jun"/>
+          <s v="28/jun"/>
+          <s v="29/jun"/>
+          <s v="30/jun"/>
+          <s v="01/jul"/>
+          <s v="02/jul"/>
+          <s v="03/jul"/>
+          <s v="04/jul"/>
+          <s v="05/jul"/>
+          <s v="06/jul"/>
+          <s v="07/jul"/>
+          <s v="08/jul"/>
+          <s v="09/jul"/>
+          <s v="10/jul"/>
+          <s v="11/jul"/>
+          <s v="12/jul"/>
+          <s v="13/jul"/>
+          <s v="14/jul"/>
+          <s v="15/jul"/>
+          <s v="16/jul"/>
+          <s v="17/jul"/>
+          <s v="18/jul"/>
+          <s v="19/jul"/>
+          <s v="20/jul"/>
+          <s v="21/jul"/>
+          <s v="22/jul"/>
+          <s v="23/jul"/>
+          <s v="24/jul"/>
+          <s v="25/jul"/>
+          <s v="26/jul"/>
+          <s v="27/jul"/>
+          <s v="28/jul"/>
+          <s v="29/jul"/>
+          <s v="30/jul"/>
+          <s v="31/jul"/>
+          <s v="01/ago"/>
+          <s v="02/ago"/>
+          <s v="03/ago"/>
+          <s v="04/ago"/>
+          <s v="05/ago"/>
+          <s v="06/ago"/>
+          <s v="07/ago"/>
+          <s v="08/ago"/>
+          <s v="09/ago"/>
+          <s v="10/ago"/>
+          <s v="11/ago"/>
+          <s v="12/ago"/>
+          <s v="13/ago"/>
+          <s v="14/ago"/>
+          <s v="15/ago"/>
+          <s v="16/ago"/>
+          <s v="17/ago"/>
+          <s v="18/ago"/>
+          <s v="19/ago"/>
+          <s v="20/ago"/>
+          <s v="21/ago"/>
+          <s v="22/ago"/>
+          <s v="23/ago"/>
+          <s v="24/ago"/>
+          <s v="25/ago"/>
+          <s v="26/ago"/>
+          <s v="27/ago"/>
+          <s v="28/ago"/>
+          <s v="29/ago"/>
+          <s v="30/ago"/>
+          <s v="31/ago"/>
+          <s v="01/set"/>
+          <s v="02/set"/>
+          <s v="03/set"/>
+          <s v="04/set"/>
+          <s v="05/set"/>
+          <s v="06/set"/>
+          <s v="07/set"/>
+          <s v="08/set"/>
+          <s v="09/set"/>
+          <s v="10/set"/>
+          <s v="11/set"/>
+          <s v="12/set"/>
+          <s v="13/set"/>
+          <s v="14/set"/>
+          <s v="15/set"/>
+          <s v="16/set"/>
+          <s v="17/set"/>
+          <s v="18/set"/>
+          <s v="19/set"/>
+          <s v="20/set"/>
+          <s v="21/set"/>
+          <s v="22/set"/>
+          <s v="23/set"/>
+          <s v="24/set"/>
+          <s v="25/set"/>
+          <s v="26/set"/>
+          <s v="27/set"/>
+          <s v="28/set"/>
+          <s v="29/set"/>
+          <s v="30/set"/>
+          <s v="01/out"/>
+          <s v="02/out"/>
+          <s v="03/out"/>
+          <s v="04/out"/>
+          <s v="05/out"/>
+          <s v="06/out"/>
+          <s v="07/out"/>
+          <s v="08/out"/>
+          <s v="09/out"/>
+          <s v="10/out"/>
+          <s v="11/out"/>
+          <s v="12/out"/>
+          <s v="13/out"/>
+          <s v="14/out"/>
+          <s v="15/out"/>
+          <s v="16/out"/>
+          <s v="17/out"/>
+          <s v="18/out"/>
+          <s v="19/out"/>
+          <s v="20/out"/>
+          <s v="21/out"/>
+          <s v="22/out"/>
+          <s v="23/out"/>
+          <s v="24/out"/>
+          <s v="25/out"/>
+          <s v="26/out"/>
+          <s v="27/out"/>
+          <s v="28/out"/>
+          <s v="29/out"/>
+          <s v="30/out"/>
+          <s v="31/out"/>
+          <s v="01/nov"/>
+          <s v="02/nov"/>
+          <s v="03/nov"/>
+          <s v="04/nov"/>
+          <s v="05/nov"/>
+          <s v="06/nov"/>
+          <s v="07/nov"/>
+          <s v="08/nov"/>
+          <s v="09/nov"/>
+          <s v="10/nov"/>
+          <s v="11/nov"/>
+          <s v="12/nov"/>
+          <s v="13/nov"/>
+          <s v="14/nov"/>
+          <s v="15/nov"/>
+          <s v="16/nov"/>
+          <s v="17/nov"/>
+          <s v="18/nov"/>
+          <s v="19/nov"/>
+          <s v="20/nov"/>
+          <s v="21/nov"/>
+          <s v="22/nov"/>
+          <s v="23/nov"/>
+          <s v="24/nov"/>
+          <s v="25/nov"/>
+          <s v="26/nov"/>
+          <s v="27/nov"/>
+          <s v="28/nov"/>
+          <s v="29/nov"/>
+          <s v="30/nov"/>
+          <s v="01/dez"/>
+          <s v="02/dez"/>
+          <s v="03/dez"/>
+          <s v="04/dez"/>
+          <s v="05/dez"/>
+          <s v="06/dez"/>
+          <s v="07/dez"/>
+          <s v="08/dez"/>
+          <s v="09/dez"/>
+          <s v="10/dez"/>
+          <s v="11/dez"/>
+          <s v="12/dez"/>
+          <s v="13/dez"/>
+          <s v="14/dez"/>
+          <s v="15/dez"/>
+          <s v="16/dez"/>
+          <s v="17/dez"/>
+          <s v="18/dez"/>
+          <s v="19/dez"/>
+          <s v="20/dez"/>
+          <s v="21/dez"/>
+          <s v="22/dez"/>
+          <s v="23/dez"/>
+          <s v="24/dez"/>
+          <s v="25/dez"/>
+          <s v="26/dez"/>
+          <s v="27/dez"/>
+          <s v="28/dez"/>
+          <s v="29/dez"/>
+          <s v="30/dez"/>
+          <s v="31/dez"/>
+          <s v="&gt;01/01/2024"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="Meses (Data)" numFmtId="0" databaseField="0">
+      <fieldGroup base="0">
+        <rangePr groupBy="months" startDate="2023-01-06T00:00:00" endDate="2024-01-01T00:00:00"/>
+        <groupItems count="14">
+          <s v="&lt;06/01/2023"/>
+          <s v="jan"/>
+          <s v="fev"/>
+          <s v="mar"/>
+          <s v="abr"/>
+          <s v="mai"/>
+          <s v="jun"/>
+          <s v="jul"/>
+          <s v="ago"/>
+          <s v="set"/>
+          <s v="out"/>
+          <s v="nov"/>
+          <s v="dez"/>
+          <s v="&gt;01/01/2024"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="120">
+  <r>
+    <x v="0"/>
+    <s v="Monitor"/>
+    <s v="Sul"/>
+    <s v="Ana"/>
+    <n v="20"/>
+    <n v="827.4"/>
+    <n v="16548"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="Monitor"/>
+    <s v="Norte"/>
+    <s v="Bruno"/>
+    <n v="1"/>
+    <n v="758.5"/>
+    <n v="758.5"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="Notebook"/>
+    <s v="Nordeste"/>
+    <s v="Daniela"/>
+    <n v="11"/>
+    <n v="2905.81"/>
+    <n v="31963.91"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="Notebook"/>
+    <s v="Centro-Oeste"/>
+    <s v="Eduardo"/>
+    <n v="6"/>
+    <n v="1855.07"/>
+    <n v="11130.42"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="Headset"/>
+    <s v="Sul"/>
+    <s v="Bruno"/>
+    <n v="7"/>
+    <n v="760.94"/>
+    <n v="5326.58"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <s v="Headset"/>
+    <s v="Nordeste"/>
+    <s v="Bruno"/>
+    <n v="14"/>
+    <n v="2505.5500000000002"/>
+    <n v="35077.700000000004"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <s v="Notebook"/>
+    <s v="Sul"/>
+    <s v="Bruno"/>
+    <n v="8"/>
+    <n v="4499.49"/>
+    <n v="35995.919999999998"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="Headset"/>
+    <s v="Sudeste"/>
+    <s v="Bruno"/>
+    <n v="16"/>
+    <n v="3923.26"/>
+    <n v="62772.160000000003"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="Teclado"/>
+    <s v="Norte"/>
+    <s v="Daniela"/>
+    <n v="15"/>
+    <n v="295.97000000000003"/>
+    <n v="4439.55"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="Mouse"/>
+    <s v="Sudeste"/>
+    <s v="Ana"/>
+    <n v="2"/>
+    <n v="2136.39"/>
+    <n v="4272.78"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="Notebook"/>
+    <s v="Sul"/>
+    <s v="Daniela"/>
+    <n v="15"/>
+    <n v="825.2"/>
+    <n v="12378"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <s v="Headset"/>
+    <s v="Norte"/>
+    <s v="Daniela"/>
+    <n v="9"/>
+    <n v="3629.92"/>
+    <n v="32669.279999999999"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <s v="Notebook"/>
+    <s v="Nordeste"/>
+    <s v="Ana"/>
+    <n v="2"/>
+    <n v="4836.45"/>
+    <n v="9672.9"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <s v="Teclado"/>
+    <s v="Centro-Oeste"/>
+    <s v="Ana"/>
+    <n v="4"/>
+    <n v="4615.97"/>
+    <n v="18463.88"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <s v="Teclado"/>
+    <s v="Sul"/>
+    <s v="Ana"/>
+    <n v="10"/>
+    <n v="2136.39"/>
+    <n v="21363.899999999998"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <s v="Monitor"/>
+    <s v="Centro-Oeste"/>
+    <s v="Bruno"/>
+    <n v="7"/>
+    <n v="573.21"/>
+    <n v="4012.4700000000003"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <s v="Teclado"/>
+    <s v="Nordeste"/>
+    <s v="Ana"/>
+    <n v="10"/>
+    <n v="1390.01"/>
+    <n v="13900.1"/>
+  </r>
+  <r>
+    <x v="16"/>
+    <s v="Headset"/>
+    <s v="Centro-Oeste"/>
+    <s v="Carlos"/>
+    <n v="14"/>
+    <n v="1651.42"/>
+    <n v="23119.88"/>
+  </r>
+  <r>
+    <x v="17"/>
+    <s v="Monitor"/>
+    <s v="Nordeste"/>
+    <s v="Bruno"/>
+    <n v="6"/>
+    <n v="2136.39"/>
+    <n v="12818.34"/>
+  </r>
+  <r>
+    <x v="18"/>
+    <s v="Teclado"/>
+    <s v="Centro-Oeste"/>
+    <s v="Ana"/>
+    <n v="9"/>
+    <n v="1348.91"/>
+    <n v="12140.19"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <s v="Mouse"/>
+    <s v="Sudeste"/>
+    <s v="Eduardo"/>
+    <n v="14"/>
+    <n v="810.29"/>
+    <n v="11344.06"/>
+  </r>
+  <r>
+    <x v="20"/>
+    <s v="Mouse"/>
+    <s v="Nordeste"/>
+    <s v="Bruno"/>
+    <n v="3"/>
+    <n v="303.69"/>
+    <n v="911.06999999999994"/>
+  </r>
+  <r>
+    <x v="21"/>
+    <s v="Headset"/>
+    <s v="Centro-Oeste"/>
+    <s v="Carlos"/>
+    <n v="16"/>
+    <n v="2166.89"/>
+    <n v="34670.239999999998"/>
+  </r>
+  <r>
+    <x v="22"/>
+    <s v="Notebook"/>
+    <s v="Sudeste"/>
+    <s v="Eduardo"/>
+    <n v="17"/>
+    <n v="3318.1"/>
+    <n v="56407.7"/>
+  </r>
+  <r>
+    <x v="23"/>
+    <s v="Teclado"/>
+    <s v="Norte"/>
+    <s v="Eduardo"/>
+    <n v="12"/>
+    <n v="3624.34"/>
+    <n v="43492.08"/>
+  </r>
+  <r>
+    <x v="23"/>
+    <s v="Mouse"/>
+    <s v="Centro-Oeste"/>
+    <s v="Daniela"/>
+    <n v="4"/>
+    <n v="1650.85"/>
+    <n v="6603.4"/>
+  </r>
+  <r>
+    <x v="24"/>
+    <s v="Monitor"/>
+    <s v="Sudeste"/>
+    <s v="Carlos"/>
+    <n v="12"/>
+    <n v="827.4"/>
+    <n v="9928.7999999999993"/>
+  </r>
+  <r>
+    <x v="25"/>
+    <s v="Mouse"/>
+    <s v="Sul"/>
+    <s v="Carlos"/>
+    <n v="13"/>
+    <n v="2643.65"/>
+    <n v="34367.450000000004"/>
+  </r>
+  <r>
+    <x v="26"/>
+    <s v="Monitor"/>
+    <s v="Nordeste"/>
+    <s v="Ana"/>
+    <n v="2"/>
+    <n v="4513.8999999999996"/>
+    <n v="9027.7999999999993"/>
+  </r>
+  <r>
+    <x v="27"/>
+    <s v="Headset"/>
+    <s v="Centro-Oeste"/>
+    <s v="Bruno"/>
+    <n v="9"/>
+    <n v="2787.97"/>
+    <n v="25091.73"/>
+  </r>
+  <r>
+    <x v="28"/>
+    <s v="Monitor"/>
+    <s v="Sudeste"/>
+    <s v="Ana"/>
+    <n v="7"/>
+    <n v="347.03"/>
+    <n v="2429.21"/>
+  </r>
+  <r>
+    <x v="29"/>
+    <s v="Headset"/>
+    <s v="Nordeste"/>
+    <s v="Ana"/>
+    <n v="17"/>
+    <n v="717.83"/>
+    <n v="12203.11"/>
+  </r>
+  <r>
+    <x v="30"/>
+    <s v="Teclado"/>
+    <s v="Sudeste"/>
+    <s v="Ana"/>
+    <n v="1"/>
+    <n v="2505.5500000000002"/>
+    <n v="2505.5500000000002"/>
+  </r>
+  <r>
+    <x v="31"/>
+    <s v="Notebook"/>
+    <s v="Norte"/>
+    <s v="Carlos"/>
+    <n v="13"/>
+    <n v="345.37"/>
+    <n v="4489.8100000000004"/>
+  </r>
+  <r>
+    <x v="32"/>
+    <s v="Notebook"/>
+    <s v="Norte"/>
+    <s v="Carlos"/>
+    <n v="7"/>
+    <n v="3587.68"/>
+    <n v="25113.759999999998"/>
+  </r>
+  <r>
+    <x v="33"/>
+    <s v="Notebook"/>
+    <s v="Nordeste"/>
+    <s v="Ana"/>
+    <n v="7"/>
+    <n v="130.11000000000001"/>
+    <n v="910.7700000000001"/>
+  </r>
+  <r>
+    <x v="34"/>
+    <s v="Teclado"/>
+    <s v="Centro-Oeste"/>
+    <s v="Daniela"/>
+    <n v="9"/>
+    <n v="130.11000000000001"/>
+    <n v="1170.9900000000002"/>
+  </r>
+  <r>
+    <x v="35"/>
+    <s v="Headset"/>
+    <s v="Sul"/>
+    <s v="Ana"/>
+    <n v="3"/>
+    <n v="3596.45"/>
+    <n v="10789.349999999999"/>
+  </r>
+  <r>
+    <x v="36"/>
+    <s v="Teclado"/>
+    <s v="Centro-Oeste"/>
+    <s v="Carlos"/>
+    <n v="1"/>
+    <n v="3908.7"/>
+    <n v="3908.7"/>
+  </r>
+  <r>
+    <x v="37"/>
+    <s v="Monitor"/>
+    <s v="Centro-Oeste"/>
+    <s v="Ana"/>
+    <n v="13"/>
+    <n v="1882.81"/>
+    <n v="24476.53"/>
+  </r>
+  <r>
+    <x v="38"/>
+    <s v="Headset"/>
+    <s v="Sudeste"/>
+    <s v="Bruno"/>
+    <n v="9"/>
+    <n v="2136.39"/>
+    <n v="19227.509999999998"/>
+  </r>
+  <r>
+    <x v="39"/>
+    <s v="Headset"/>
+    <s v="Centro-Oeste"/>
+    <s v="Ana"/>
+    <n v="8"/>
+    <n v="482.06"/>
+    <n v="3856.48"/>
+  </r>
+  <r>
+    <x v="40"/>
+    <s v="Monitor"/>
+    <s v="Norte"/>
+    <s v="Daniela"/>
+    <n v="20"/>
+    <n v="3554.54"/>
+    <n v="71090.8"/>
+  </r>
+  <r>
+    <x v="41"/>
+    <s v="Teclado"/>
+    <s v="Centro-Oeste"/>
+    <s v="Carlos"/>
+    <n v="6"/>
+    <n v="2049.16"/>
+    <n v="12294.96"/>
+  </r>
+  <r>
+    <x v="42"/>
+    <s v="Monitor"/>
+    <s v="Centro-Oeste"/>
+    <s v="Eduardo"/>
+    <n v="2"/>
+    <n v="1168.19"/>
+    <n v="2336.38"/>
+  </r>
+  <r>
+    <x v="43"/>
+    <s v="Notebook"/>
+    <s v="Norte"/>
+    <s v="Ana"/>
+    <n v="10"/>
+    <n v="3923.26"/>
+    <n v="39232.600000000006"/>
+  </r>
+  <r>
+    <x v="44"/>
+    <s v="Teclado"/>
+    <s v="Sul"/>
+    <s v="Daniela"/>
+    <n v="3"/>
+    <n v="4513.8999999999996"/>
+    <n v="13541.699999999999"/>
+  </r>
+  <r>
+    <x v="45"/>
+    <s v="Notebook"/>
+    <s v="Sudeste"/>
+    <s v="Daniela"/>
+    <n v="14"/>
+    <n v="1401.69"/>
+    <n v="19623.66"/>
+  </r>
+  <r>
+    <x v="45"/>
+    <s v="Teclado"/>
+    <s v="Nordeste"/>
+    <s v="Carlos"/>
+    <n v="10"/>
+    <n v="807.99"/>
+    <n v="8079.9"/>
+  </r>
+  <r>
+    <x v="45"/>
+    <s v="Mouse"/>
+    <s v="Norte"/>
+    <s v="Daniela"/>
+    <n v="10"/>
+    <n v="2016.18"/>
+    <n v="20161.8"/>
+  </r>
+  <r>
+    <x v="46"/>
+    <s v="Teclado"/>
+    <s v="Sul"/>
+    <s v="Ana"/>
+    <n v="20"/>
+    <n v="2505.5500000000002"/>
+    <n v="50111"/>
+  </r>
+  <r>
+    <x v="47"/>
+    <s v="Mouse"/>
+    <s v="Sul"/>
+    <s v="Ana"/>
+    <n v="3"/>
+    <n v="573.21"/>
+    <n v="1719.63"/>
+  </r>
+  <r>
+    <x v="48"/>
+    <s v="Headset"/>
+    <s v="Nordeste"/>
+    <s v="Bruno"/>
+    <n v="8"/>
+    <n v="4961.6000000000004"/>
+    <n v="39692.800000000003"/>
+  </r>
+  <r>
+    <x v="49"/>
+    <s v="Headset"/>
+    <s v="Centro-Oeste"/>
+    <s v="Ana"/>
+    <n v="18"/>
+    <n v="1424.69"/>
+    <n v="25644.420000000002"/>
+  </r>
+  <r>
+    <x v="50"/>
+    <s v="Teclado"/>
+    <s v="Sudeste"/>
+    <s v="Daniela"/>
+    <n v="7"/>
+    <n v="2873.97"/>
+    <n v="20117.789999999997"/>
+  </r>
+  <r>
+    <x v="50"/>
+    <s v="Teclado"/>
+    <s v="Norte"/>
+    <s v="Bruno"/>
+    <n v="10"/>
+    <n v="2275.71"/>
+    <n v="22757.1"/>
+  </r>
+  <r>
+    <x v="51"/>
+    <s v="Headset"/>
+    <s v="Sudeste"/>
+    <s v="Ana"/>
+    <n v="8"/>
+    <n v="4913.28"/>
+    <n v="39306.239999999998"/>
+  </r>
+  <r>
+    <x v="52"/>
+    <s v="Headset"/>
+    <s v="Centro-Oeste"/>
+    <s v="Daniela"/>
+    <n v="11"/>
+    <n v="1650.85"/>
+    <n v="18159.349999999999"/>
+  </r>
+  <r>
+    <x v="53"/>
+    <s v="Notebook"/>
+    <s v="Sudeste"/>
+    <s v="Eduardo"/>
+    <n v="17"/>
+    <n v="2415.0700000000002"/>
+    <n v="41056.19"/>
+  </r>
+  <r>
+    <x v="54"/>
+    <s v="Mouse"/>
+    <s v="Norte"/>
+    <s v="Ana"/>
+    <n v="20"/>
+    <n v="1882.81"/>
+    <n v="37656.199999999997"/>
+  </r>
+  <r>
+    <x v="55"/>
+    <s v="Notebook"/>
+    <s v="Sudeste"/>
+    <s v="Ana"/>
+    <n v="5"/>
+    <n v="4332.25"/>
+    <n v="21661.25"/>
+  </r>
+  <r>
+    <x v="56"/>
+    <s v="Teclado"/>
+    <s v="Sul"/>
+    <s v="Eduardo"/>
+    <n v="7"/>
+    <n v="130.11000000000001"/>
+    <n v="910.7700000000001"/>
+  </r>
+  <r>
+    <x v="57"/>
+    <s v="Mouse"/>
+    <s v="Sudeste"/>
+    <s v="Daniela"/>
+    <n v="3"/>
+    <n v="1650.85"/>
+    <n v="4952.5499999999993"/>
+  </r>
+  <r>
+    <x v="57"/>
+    <s v="Monitor"/>
+    <s v="Nordeste"/>
+    <s v="Carlos"/>
+    <n v="1"/>
+    <n v="827.4"/>
+    <n v="827.4"/>
+  </r>
+  <r>
+    <x v="58"/>
+    <s v="Notebook"/>
+    <s v="Nordeste"/>
+    <s v="Eduardo"/>
+    <n v="18"/>
+    <n v="2505.5500000000002"/>
+    <n v="45099.9"/>
+  </r>
+  <r>
+    <x v="58"/>
+    <s v="Notebook"/>
+    <s v="Centro-Oeste"/>
+    <s v="Daniela"/>
+    <n v="14"/>
+    <n v="807.99"/>
+    <n v="11311.86"/>
+  </r>
+  <r>
+    <x v="59"/>
+    <s v="Monitor"/>
+    <s v="Norte"/>
+    <s v="Eduardo"/>
+    <n v="14"/>
+    <n v="3139.25"/>
+    <n v="43949.5"/>
+  </r>
+  <r>
+    <x v="60"/>
+    <s v="Mouse"/>
+    <s v="Sul"/>
+    <s v="Eduardo"/>
+    <n v="17"/>
+    <n v="573.21"/>
+    <n v="9744.57"/>
+  </r>
+  <r>
+    <x v="61"/>
+    <s v="Headset"/>
+    <s v="Nordeste"/>
+    <s v="Daniela"/>
+    <n v="3"/>
+    <n v="1650.85"/>
+    <n v="4952.5499999999993"/>
+  </r>
+  <r>
+    <x v="62"/>
+    <s v="Mouse"/>
+    <s v="Nordeste"/>
+    <s v="Eduardo"/>
+    <n v="16"/>
+    <n v="1211.28"/>
+    <n v="19380.48"/>
+  </r>
+  <r>
+    <x v="63"/>
+    <s v="Notebook"/>
+    <s v="Nordeste"/>
+    <s v="Ana"/>
+    <n v="11"/>
+    <n v="295.97000000000003"/>
+    <n v="3255.67"/>
+  </r>
+  <r>
+    <x v="64"/>
+    <s v="Teclado"/>
+    <s v="Nordeste"/>
+    <s v="Ana"/>
+    <n v="17"/>
+    <n v="4390.2700000000004"/>
+    <n v="74634.590000000011"/>
+  </r>
+  <r>
+    <x v="65"/>
+    <s v="Notebook"/>
+    <s v="Nordeste"/>
+    <s v="Bruno"/>
+    <n v="20"/>
+    <n v="2643.65"/>
+    <n v="52873"/>
+  </r>
+  <r>
+    <x v="66"/>
+    <s v="Headset"/>
+    <s v="Sudeste"/>
+    <s v="Daniela"/>
+    <n v="16"/>
+    <n v="4615.97"/>
+    <n v="73855.520000000004"/>
+  </r>
+  <r>
+    <x v="67"/>
+    <s v="Teclado"/>
+    <s v="Sudeste"/>
+    <s v="Bruno"/>
+    <n v="6"/>
+    <n v="3908.7"/>
+    <n v="23452.199999999997"/>
+  </r>
+  <r>
+    <x v="67"/>
+    <s v="Notebook"/>
+    <s v="Sudeste"/>
+    <s v="Bruno"/>
+    <n v="11"/>
+    <n v="1651.42"/>
+    <n v="18165.620000000003"/>
+  </r>
+  <r>
+    <x v="68"/>
+    <s v="Headset"/>
+    <s v="Centro-Oeste"/>
+    <s v="Eduardo"/>
+    <n v="5"/>
+    <n v="3110.71"/>
+    <n v="15553.55"/>
+  </r>
+  <r>
+    <x v="69"/>
+    <s v="Notebook"/>
+    <s v="Centro-Oeste"/>
+    <s v="Carlos"/>
+    <n v="4"/>
+    <n v="1168.19"/>
+    <n v="4672.76"/>
+  </r>
+  <r>
+    <x v="70"/>
+    <s v="Teclado"/>
+    <s v="Centro-Oeste"/>
+    <s v="Carlos"/>
+    <n v="19"/>
+    <n v="2239.29"/>
+    <n v="42546.51"/>
+  </r>
+  <r>
+    <x v="71"/>
+    <s v="Monitor"/>
+    <s v="Sul"/>
+    <s v="Carlos"/>
+    <n v="8"/>
+    <n v="3822.16"/>
+    <n v="30577.279999999999"/>
+  </r>
+  <r>
+    <x v="71"/>
+    <s v="Teclado"/>
+    <s v="Norte"/>
+    <s v="Daniela"/>
+    <n v="5"/>
+    <n v="1168.19"/>
+    <n v="5840.9500000000007"/>
+  </r>
+  <r>
+    <x v="72"/>
+    <s v="Notebook"/>
+    <s v="Centro-Oeste"/>
+    <s v="Daniela"/>
+    <n v="14"/>
+    <n v="4513.8999999999996"/>
+    <n v="63194.599999999991"/>
+  </r>
+  <r>
+    <x v="73"/>
+    <s v="Notebook"/>
+    <s v="Nordeste"/>
+    <s v="Ana"/>
+    <n v="8"/>
+    <n v="2077.83"/>
+    <n v="16622.64"/>
+  </r>
+  <r>
+    <x v="73"/>
+    <s v="Teclado"/>
+    <s v="Sul"/>
+    <s v="Carlos"/>
+    <n v="3"/>
+    <n v="4587.28"/>
+    <n v="13761.84"/>
+  </r>
+  <r>
+    <x v="74"/>
+    <s v="Notebook"/>
+    <s v="Norte"/>
+    <s v="Bruno"/>
+    <n v="2"/>
+    <n v="90.35"/>
+    <n v="180.7"/>
+  </r>
+  <r>
+    <x v="75"/>
+    <s v="Mouse"/>
+    <s v="Norte"/>
+    <s v="Ana"/>
+    <n v="13"/>
+    <n v="550.23"/>
+    <n v="7152.99"/>
+  </r>
+  <r>
+    <x v="76"/>
+    <s v="Teclado"/>
+    <s v="Sudeste"/>
+    <s v="Carlos"/>
+    <n v="8"/>
+    <n v="3318.1"/>
+    <n v="26544.799999999999"/>
+  </r>
+  <r>
+    <x v="77"/>
+    <s v="Notebook"/>
+    <s v="Nordeste"/>
+    <s v="Daniela"/>
+    <n v="18"/>
+    <n v="2450.65"/>
+    <n v="44111.700000000004"/>
+  </r>
+  <r>
+    <x v="78"/>
+    <s v="Teclado"/>
+    <s v="Nordeste"/>
+    <s v="Bruno"/>
+    <n v="16"/>
+    <n v="1168.19"/>
+    <n v="18691.04"/>
+  </r>
+  <r>
+    <x v="78"/>
+    <s v="Teclado"/>
+    <s v="Nordeste"/>
+    <s v="Daniela"/>
+    <n v="9"/>
+    <n v="1650.85"/>
+    <n v="14857.65"/>
+  </r>
+  <r>
+    <x v="79"/>
+    <s v="Notebook"/>
+    <s v="Centro-Oeste"/>
+    <s v="Daniela"/>
+    <n v="5"/>
+    <n v="1168.19"/>
+    <n v="5840.9500000000007"/>
+  </r>
+  <r>
+    <x v="80"/>
+    <s v="Notebook"/>
+    <s v="Centro-Oeste"/>
+    <s v="Carlos"/>
+    <n v="5"/>
+    <n v="573.21"/>
+    <n v="2866.05"/>
+  </r>
+  <r>
+    <x v="81"/>
+    <s v="Notebook"/>
+    <s v="Centro-Oeste"/>
+    <s v="Carlos"/>
+    <n v="6"/>
+    <n v="3587.68"/>
+    <n v="21526.079999999998"/>
+  </r>
+  <r>
+    <x v="81"/>
+    <s v="Teclado"/>
+    <s v="Norte"/>
+    <s v="Daniela"/>
+    <n v="17"/>
+    <n v="2016.18"/>
+    <n v="34275.06"/>
+  </r>
+  <r>
+    <x v="82"/>
+    <s v="Mouse"/>
+    <s v="Nordeste"/>
+    <s v="Bruno"/>
+    <n v="2"/>
+    <n v="4499.49"/>
+    <n v="8998.98"/>
+  </r>
+  <r>
+    <x v="83"/>
+    <s v="Teclado"/>
+    <s v="Sul"/>
+    <s v="Eduardo"/>
+    <n v="11"/>
+    <n v="2465.4499999999998"/>
+    <n v="27119.949999999997"/>
+  </r>
+  <r>
+    <x v="84"/>
+    <s v="Teclado"/>
+    <s v="Sul"/>
+    <s v="Ana"/>
+    <n v="14"/>
+    <n v="313.20999999999998"/>
+    <n v="4384.9399999999996"/>
+  </r>
+  <r>
+    <x v="85"/>
+    <s v="Monitor"/>
+    <s v="Nordeste"/>
+    <s v="Carlos"/>
+    <n v="19"/>
+    <n v="1108.71"/>
+    <n v="21065.49"/>
+  </r>
+  <r>
+    <x v="86"/>
+    <s v="Notebook"/>
+    <s v="Centro-Oeste"/>
+    <s v="Bruno"/>
+    <n v="17"/>
+    <n v="179.65"/>
+    <n v="3054.05"/>
+  </r>
+  <r>
+    <x v="87"/>
+    <s v="Headset"/>
+    <s v="Centro-Oeste"/>
+    <s v="Bruno"/>
+    <n v="15"/>
+    <n v="1651.42"/>
+    <n v="24771.300000000003"/>
+  </r>
+  <r>
+    <x v="88"/>
+    <s v="Teclado"/>
+    <s v="Centro-Oeste"/>
+    <s v="Ana"/>
+    <n v="2"/>
+    <n v="827.4"/>
+    <n v="1654.8"/>
+  </r>
+  <r>
+    <x v="88"/>
+    <s v="Mouse"/>
+    <s v="Sul"/>
+    <s v="Eduardo"/>
+    <n v="11"/>
+    <n v="702.91"/>
+    <n v="7732.0099999999993"/>
+  </r>
+  <r>
+    <x v="89"/>
+    <s v="Monitor"/>
+    <s v="Norte"/>
+    <s v="Daniela"/>
+    <n v="12"/>
+    <n v="3318.1"/>
+    <n v="39817.199999999997"/>
+  </r>
+  <r>
+    <x v="90"/>
+    <s v="Teclado"/>
+    <s v="Sudeste"/>
+    <s v="Ana"/>
+    <n v="4"/>
+    <n v="827.4"/>
+    <n v="3309.6"/>
+  </r>
+  <r>
+    <x v="91"/>
+    <s v="Teclado"/>
+    <s v="Sudeste"/>
+    <s v="Carlos"/>
+    <n v="5"/>
+    <n v="4499.49"/>
+    <n v="22497.449999999997"/>
+  </r>
+  <r>
+    <x v="92"/>
+    <s v="Headset"/>
+    <s v="Norte"/>
+    <s v="Carlos"/>
+    <n v="6"/>
+    <n v="3218.22"/>
+    <n v="19309.32"/>
+  </r>
+  <r>
+    <x v="93"/>
+    <s v="Teclado"/>
+    <s v="Norte"/>
+    <s v="Eduardo"/>
+    <n v="12"/>
+    <n v="1417.08"/>
+    <n v="17004.96"/>
+  </r>
+  <r>
+    <x v="94"/>
+    <s v="Headset"/>
+    <s v="Sudeste"/>
+    <s v="Carlos"/>
+    <n v="1"/>
+    <n v="573.21"/>
+    <n v="573.21"/>
+  </r>
+  <r>
+    <x v="94"/>
+    <s v="Notebook"/>
+    <s v="Nordeste"/>
+    <s v="Carlos"/>
+    <n v="15"/>
+    <n v="573.21"/>
+    <n v="8598.1500000000015"/>
+  </r>
+  <r>
+    <x v="95"/>
+    <s v="Notebook"/>
+    <s v="Sul"/>
+    <s v="Ana"/>
+    <n v="19"/>
+    <n v="2136.39"/>
+    <n v="40591.409999999996"/>
+  </r>
+  <r>
+    <x v="96"/>
+    <s v="Headset"/>
+    <s v="Sudeste"/>
+    <s v="Ana"/>
+    <n v="8"/>
+    <n v="1966.9"/>
+    <n v="15735.2"/>
+  </r>
+  <r>
+    <x v="97"/>
+    <s v="Headset"/>
+    <s v="Norte"/>
+    <s v="Bruno"/>
+    <n v="16"/>
+    <n v="1651.42"/>
+    <n v="26422.720000000001"/>
+  </r>
+  <r>
+    <x v="98"/>
+    <s v="Headset"/>
+    <s v="Nordeste"/>
+    <s v="Bruno"/>
+    <n v="17"/>
+    <n v="827.4"/>
+    <n v="14065.8"/>
+  </r>
+  <r>
+    <x v="99"/>
+    <s v="Teclado"/>
+    <s v="Centro-Oeste"/>
+    <s v="Ana"/>
+    <n v="3"/>
+    <n v="2649.97"/>
+    <n v="7949.91"/>
+  </r>
+  <r>
+    <x v="100"/>
+    <s v="Mouse"/>
+    <s v="Centro-Oeste"/>
+    <s v="Bruno"/>
+    <n v="9"/>
+    <n v="3523.1"/>
+    <n v="31707.899999999998"/>
+  </r>
+  <r>
+    <x v="100"/>
+    <s v="Teclado"/>
+    <s v="Centro-Oeste"/>
+    <s v="Daniela"/>
+    <n v="3"/>
+    <n v="1650.85"/>
+    <n v="4952.5499999999993"/>
+  </r>
+  <r>
+    <x v="101"/>
+    <s v="Monitor"/>
+    <s v="Norte"/>
+    <s v="Ana"/>
+    <n v="5"/>
+    <n v="670.54"/>
+    <n v="3352.7"/>
+  </r>
+  <r>
+    <x v="102"/>
+    <s v="Mouse"/>
+    <s v="Sudeste"/>
+    <s v="Carlos"/>
+    <n v="1"/>
+    <n v="4499.49"/>
+    <n v="4499.49"/>
+  </r>
+  <r>
+    <x v="103"/>
+    <s v="Headset"/>
+    <s v="Centro-Oeste"/>
+    <s v="Carlos"/>
+    <n v="19"/>
+    <n v="380.24"/>
+    <n v="7224.56"/>
+  </r>
+  <r>
+    <x v="104"/>
+    <s v="Monitor"/>
+    <s v="Centro-Oeste"/>
+    <s v="Ana"/>
+    <n v="10"/>
+    <n v="313.20999999999998"/>
+    <n v="3132.1"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1E649CAC-622A-4C96-9AD2-8FB8047D97D3}" name="Tabela dinâmica3" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="Período em Meses">
+  <location ref="B8:C21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField axis="axisRow" numFmtId="14" showAll="0">
+      <items count="106">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="369">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item sd="0" x="14"/>
+        <item sd="0" x="15"/>
+        <item sd="0" x="16"/>
+        <item sd="0" x="17"/>
+        <item sd="0" x="18"/>
+        <item sd="0" x="19"/>
+        <item sd="0" x="20"/>
+        <item sd="0" x="21"/>
+        <item sd="0" x="22"/>
+        <item sd="0" x="23"/>
+        <item sd="0" x="24"/>
+        <item sd="0" x="25"/>
+        <item sd="0" x="26"/>
+        <item sd="0" x="27"/>
+        <item sd="0" x="28"/>
+        <item sd="0" x="29"/>
+        <item sd="0" x="30"/>
+        <item sd="0" x="31"/>
+        <item sd="0" x="32"/>
+        <item sd="0" x="33"/>
+        <item sd="0" x="34"/>
+        <item sd="0" x="35"/>
+        <item sd="0" x="36"/>
+        <item sd="0" x="37"/>
+        <item sd="0" x="38"/>
+        <item sd="0" x="39"/>
+        <item sd="0" x="40"/>
+        <item sd="0" x="41"/>
+        <item sd="0" x="42"/>
+        <item sd="0" x="43"/>
+        <item sd="0" x="44"/>
+        <item sd="0" x="45"/>
+        <item sd="0" x="46"/>
+        <item sd="0" x="47"/>
+        <item sd="0" x="48"/>
+        <item sd="0" x="49"/>
+        <item sd="0" x="50"/>
+        <item sd="0" x="51"/>
+        <item sd="0" x="52"/>
+        <item sd="0" x="53"/>
+        <item sd="0" x="54"/>
+        <item sd="0" x="55"/>
+        <item sd="0" x="56"/>
+        <item sd="0" x="57"/>
+        <item sd="0" x="58"/>
+        <item sd="0" x="59"/>
+        <item sd="0" x="60"/>
+        <item sd="0" x="61"/>
+        <item sd="0" x="62"/>
+        <item sd="0" x="63"/>
+        <item sd="0" x="64"/>
+        <item sd="0" x="65"/>
+        <item sd="0" x="66"/>
+        <item sd="0" x="67"/>
+        <item sd="0" x="68"/>
+        <item sd="0" x="69"/>
+        <item sd="0" x="70"/>
+        <item sd="0" x="71"/>
+        <item sd="0" x="72"/>
+        <item sd="0" x="73"/>
+        <item sd="0" x="74"/>
+        <item sd="0" x="75"/>
+        <item sd="0" x="76"/>
+        <item sd="0" x="77"/>
+        <item sd="0" x="78"/>
+        <item sd="0" x="79"/>
+        <item sd="0" x="80"/>
+        <item sd="0" x="81"/>
+        <item sd="0" x="82"/>
+        <item sd="0" x="83"/>
+        <item sd="0" x="84"/>
+        <item sd="0" x="85"/>
+        <item sd="0" x="86"/>
+        <item sd="0" x="87"/>
+        <item sd="0" x="88"/>
+        <item sd="0" x="89"/>
+        <item sd="0" x="90"/>
+        <item sd="0" x="91"/>
+        <item sd="0" x="92"/>
+        <item sd="0" x="93"/>
+        <item sd="0" x="94"/>
+        <item sd="0" x="95"/>
+        <item sd="0" x="96"/>
+        <item sd="0" x="97"/>
+        <item sd="0" x="98"/>
+        <item sd="0" x="99"/>
+        <item sd="0" x="100"/>
+        <item sd="0" x="101"/>
+        <item sd="0" x="102"/>
+        <item sd="0" x="103"/>
+        <item sd="0" x="104"/>
+        <item sd="0" x="105"/>
+        <item sd="0" x="106"/>
+        <item sd="0" x="107"/>
+        <item sd="0" x="108"/>
+        <item sd="0" x="109"/>
+        <item sd="0" x="110"/>
+        <item sd="0" x="111"/>
+        <item sd="0" x="112"/>
+        <item sd="0" x="113"/>
+        <item sd="0" x="114"/>
+        <item sd="0" x="115"/>
+        <item sd="0" x="116"/>
+        <item sd="0" x="117"/>
+        <item sd="0" x="118"/>
+        <item sd="0" x="119"/>
+        <item sd="0" x="120"/>
+        <item sd="0" x="121"/>
+        <item sd="0" x="122"/>
+        <item sd="0" x="123"/>
+        <item sd="0" x="124"/>
+        <item sd="0" x="125"/>
+        <item sd="0" x="126"/>
+        <item sd="0" x="127"/>
+        <item sd="0" x="128"/>
+        <item sd="0" x="129"/>
+        <item sd="0" x="130"/>
+        <item sd="0" x="131"/>
+        <item sd="0" x="132"/>
+        <item sd="0" x="133"/>
+        <item sd="0" x="134"/>
+        <item sd="0" x="135"/>
+        <item sd="0" x="136"/>
+        <item sd="0" x="137"/>
+        <item sd="0" x="138"/>
+        <item sd="0" x="139"/>
+        <item sd="0" x="140"/>
+        <item sd="0" x="141"/>
+        <item sd="0" x="142"/>
+        <item sd="0" x="143"/>
+        <item sd="0" x="144"/>
+        <item sd="0" x="145"/>
+        <item sd="0" x="146"/>
+        <item sd="0" x="147"/>
+        <item sd="0" x="148"/>
+        <item sd="0" x="149"/>
+        <item sd="0" x="150"/>
+        <item sd="0" x="151"/>
+        <item sd="0" x="152"/>
+        <item sd="0" x="153"/>
+        <item sd="0" x="154"/>
+        <item sd="0" x="155"/>
+        <item sd="0" x="156"/>
+        <item sd="0" x="157"/>
+        <item sd="0" x="158"/>
+        <item sd="0" x="159"/>
+        <item sd="0" x="160"/>
+        <item sd="0" x="161"/>
+        <item sd="0" x="162"/>
+        <item sd="0" x="163"/>
+        <item sd="0" x="164"/>
+        <item sd="0" x="165"/>
+        <item sd="0" x="166"/>
+        <item sd="0" x="167"/>
+        <item sd="0" x="168"/>
+        <item sd="0" x="169"/>
+        <item sd="0" x="170"/>
+        <item sd="0" x="171"/>
+        <item sd="0" x="172"/>
+        <item sd="0" x="173"/>
+        <item sd="0" x="174"/>
+        <item sd="0" x="175"/>
+        <item sd="0" x="176"/>
+        <item sd="0" x="177"/>
+        <item sd="0" x="178"/>
+        <item sd="0" x="179"/>
+        <item sd="0" x="180"/>
+        <item sd="0" x="181"/>
+        <item sd="0" x="182"/>
+        <item sd="0" x="183"/>
+        <item sd="0" x="184"/>
+        <item sd="0" x="185"/>
+        <item sd="0" x="186"/>
+        <item sd="0" x="187"/>
+        <item sd="0" x="188"/>
+        <item sd="0" x="189"/>
+        <item sd="0" x="190"/>
+        <item sd="0" x="191"/>
+        <item sd="0" x="192"/>
+        <item sd="0" x="193"/>
+        <item sd="0" x="194"/>
+        <item sd="0" x="195"/>
+        <item sd="0" x="196"/>
+        <item sd="0" x="197"/>
+        <item sd="0" x="198"/>
+        <item sd="0" x="199"/>
+        <item sd="0" x="200"/>
+        <item sd="0" x="201"/>
+        <item sd="0" x="202"/>
+        <item sd="0" x="203"/>
+        <item sd="0" x="204"/>
+        <item sd="0" x="205"/>
+        <item sd="0" x="206"/>
+        <item sd="0" x="207"/>
+        <item sd="0" x="208"/>
+        <item sd="0" x="209"/>
+        <item sd="0" x="210"/>
+        <item sd="0" x="211"/>
+        <item sd="0" x="212"/>
+        <item sd="0" x="213"/>
+        <item sd="0" x="214"/>
+        <item sd="0" x="215"/>
+        <item sd="0" x="216"/>
+        <item sd="0" x="217"/>
+        <item sd="0" x="218"/>
+        <item sd="0" x="219"/>
+        <item sd="0" x="220"/>
+        <item sd="0" x="221"/>
+        <item sd="0" x="222"/>
+        <item sd="0" x="223"/>
+        <item sd="0" x="224"/>
+        <item sd="0" x="225"/>
+        <item sd="0" x="226"/>
+        <item sd="0" x="227"/>
+        <item sd="0" x="228"/>
+        <item sd="0" x="229"/>
+        <item sd="0" x="230"/>
+        <item sd="0" x="231"/>
+        <item sd="0" x="232"/>
+        <item sd="0" x="233"/>
+        <item sd="0" x="234"/>
+        <item sd="0" x="235"/>
+        <item sd="0" x="236"/>
+        <item sd="0" x="237"/>
+        <item sd="0" x="238"/>
+        <item sd="0" x="239"/>
+        <item sd="0" x="240"/>
+        <item sd="0" x="241"/>
+        <item sd="0" x="242"/>
+        <item sd="0" x="243"/>
+        <item sd="0" x="244"/>
+        <item sd="0" x="245"/>
+        <item sd="0" x="246"/>
+        <item sd="0" x="247"/>
+        <item sd="0" x="248"/>
+        <item sd="0" x="249"/>
+        <item sd="0" x="250"/>
+        <item sd="0" x="251"/>
+        <item sd="0" x="252"/>
+        <item sd="0" x="253"/>
+        <item sd="0" x="254"/>
+        <item sd="0" x="255"/>
+        <item sd="0" x="256"/>
+        <item sd="0" x="257"/>
+        <item sd="0" x="258"/>
+        <item sd="0" x="259"/>
+        <item sd="0" x="260"/>
+        <item sd="0" x="261"/>
+        <item sd="0" x="262"/>
+        <item sd="0" x="263"/>
+        <item sd="0" x="264"/>
+        <item sd="0" x="265"/>
+        <item sd="0" x="266"/>
+        <item sd="0" x="267"/>
+        <item sd="0" x="268"/>
+        <item sd="0" x="269"/>
+        <item sd="0" x="270"/>
+        <item sd="0" x="271"/>
+        <item sd="0" x="272"/>
+        <item sd="0" x="273"/>
+        <item sd="0" x="274"/>
+        <item sd="0" x="275"/>
+        <item sd="0" x="276"/>
+        <item sd="0" x="277"/>
+        <item sd="0" x="278"/>
+        <item sd="0" x="279"/>
+        <item sd="0" x="280"/>
+        <item sd="0" x="281"/>
+        <item sd="0" x="282"/>
+        <item sd="0" x="283"/>
+        <item sd="0" x="284"/>
+        <item sd="0" x="285"/>
+        <item sd="0" x="286"/>
+        <item sd="0" x="287"/>
+        <item sd="0" x="288"/>
+        <item sd="0" x="289"/>
+        <item sd="0" x="290"/>
+        <item sd="0" x="291"/>
+        <item sd="0" x="292"/>
+        <item sd="0" x="293"/>
+        <item sd="0" x="294"/>
+        <item sd="0" x="295"/>
+        <item sd="0" x="296"/>
+        <item sd="0" x="297"/>
+        <item sd="0" x="298"/>
+        <item sd="0" x="299"/>
+        <item sd="0" x="300"/>
+        <item sd="0" x="301"/>
+        <item sd="0" x="302"/>
+        <item sd="0" x="303"/>
+        <item sd="0" x="304"/>
+        <item sd="0" x="305"/>
+        <item sd="0" x="306"/>
+        <item sd="0" x="307"/>
+        <item sd="0" x="308"/>
+        <item sd="0" x="309"/>
+        <item sd="0" x="310"/>
+        <item sd="0" x="311"/>
+        <item sd="0" x="312"/>
+        <item sd="0" x="313"/>
+        <item sd="0" x="314"/>
+        <item sd="0" x="315"/>
+        <item sd="0" x="316"/>
+        <item sd="0" x="317"/>
+        <item sd="0" x="318"/>
+        <item sd="0" x="319"/>
+        <item sd="0" x="320"/>
+        <item sd="0" x="321"/>
+        <item sd="0" x="322"/>
+        <item sd="0" x="323"/>
+        <item sd="0" x="324"/>
+        <item sd="0" x="325"/>
+        <item sd="0" x="326"/>
+        <item sd="0" x="327"/>
+        <item sd="0" x="328"/>
+        <item sd="0" x="329"/>
+        <item sd="0" x="330"/>
+        <item sd="0" x="331"/>
+        <item sd="0" x="332"/>
+        <item sd="0" x="333"/>
+        <item sd="0" x="334"/>
+        <item sd="0" x="335"/>
+        <item sd="0" x="336"/>
+        <item sd="0" x="337"/>
+        <item sd="0" x="338"/>
+        <item sd="0" x="339"/>
+        <item sd="0" x="340"/>
+        <item sd="0" x="341"/>
+        <item sd="0" x="342"/>
+        <item sd="0" x="343"/>
+        <item sd="0" x="344"/>
+        <item sd="0" x="345"/>
+        <item sd="0" x="346"/>
+        <item sd="0" x="347"/>
+        <item sd="0" x="348"/>
+        <item sd="0" x="349"/>
+        <item sd="0" x="350"/>
+        <item sd="0" x="351"/>
+        <item sd="0" x="352"/>
+        <item sd="0" x="353"/>
+        <item sd="0" x="354"/>
+        <item sd="0" x="355"/>
+        <item sd="0" x="356"/>
+        <item sd="0" x="357"/>
+        <item sd="0" x="358"/>
+        <item sd="0" x="359"/>
+        <item sd="0" x="360"/>
+        <item sd="0" x="361"/>
+        <item sd="0" x="362"/>
+        <item sd="0" x="363"/>
+        <item sd="0" x="364"/>
+        <item sd="0" x="365"/>
+        <item sd="0" x="366"/>
+        <item sd="0" x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="15">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="3">
+    <field x="8"/>
+    <field x="7"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Soma de Receita" fld="6" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <formats count="14">
+    <format dxfId="26">
+      <pivotArea field="8" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="25">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="23">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="8" count="1">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="21">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="8" count="1">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="19">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="8" count="1">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="17">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="8" count="1">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="15">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="8" count="1">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="13">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="8" count="1">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="11">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="8" count="1">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="9">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="8" count="1">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="7">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="8" count="1">
+            <x v="9"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="5">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="8" count="1">
+            <x v="10"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="3">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="8" count="1">
+            <x v="11"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="1">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="8" count="1">
+            <x v="12"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="1">
+    <chartFormat chart="1" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -455,259 +4130,255 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I122"/>
+  <dimension ref="A1:I123"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.140625" customWidth="1"/>
-    <col min="2" max="2" width="17.140625" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="18.140625" customWidth="1"/>
-    <col min="6" max="6" width="21" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="20.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>44932</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="5">
-        <v>20</v>
-      </c>
-      <c r="F2" s="6">
-        <v>827.4</v>
-      </c>
-      <c r="G2" s="6">
-        <f>F2*E2</f>
-        <v>16548</v>
-      </c>
-      <c r="I2" s="1"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>44933</v>
+        <v>44932</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" s="5">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F3" s="6">
-        <v>758.5</v>
+        <v>827.4</v>
       </c>
       <c r="G3" s="6">
-        <f>F3*E3</f>
-        <v>758.5</v>
+        <f t="shared" ref="G3:G34" si="0">F3*E3</f>
+        <v>16548</v>
       </c>
       <c r="I3" s="1"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>44937</v>
+        <v>44933</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E4" s="5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F4" s="6">
-        <v>2905.81</v>
+        <v>758.5</v>
       </c>
       <c r="G4" s="6">
-        <f>F4*E4</f>
-        <v>31963.91</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>758.5</v>
+      </c>
+      <c r="I4" s="1"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>44938</v>
+        <v>44937</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E5" s="5">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F5" s="6">
-        <v>1855.07</v>
+        <v>2905.81</v>
       </c>
       <c r="G5" s="6">
-        <f>F5*E5</f>
-        <v>11130.42</v>
+        <f t="shared" si="0"/>
+        <v>31963.91</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>44943</v>
+        <v>44938</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E6" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" s="6">
-        <v>760.94</v>
+        <v>1855.07</v>
       </c>
       <c r="G6" s="6">
-        <f>F6*E6</f>
-        <v>5326.58</v>
+        <f t="shared" si="0"/>
+        <v>11130.42</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>44944</v>
+        <v>44943</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
       </c>
       <c r="E7" s="5">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F7" s="6">
-        <v>2505.5500000000002</v>
+        <v>760.94</v>
       </c>
       <c r="G7" s="6">
-        <f>F7*E7</f>
-        <v>35077.700000000004</v>
+        <f t="shared" si="0"/>
+        <v>5326.58</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>44947</v>
+        <v>44944</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="5">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F8" s="6">
-        <v>4499.49</v>
+        <v>2505.5500000000002</v>
       </c>
       <c r="G8" s="6">
-        <f>F8*E8</f>
-        <v>35995.919999999998</v>
+        <f t="shared" si="0"/>
+        <v>35077.700000000004</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>44954</v>
+        <v>44947</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
       </c>
       <c r="E9" s="5">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F9" s="6">
-        <v>3923.26</v>
+        <v>4499.49</v>
       </c>
       <c r="G9" s="6">
-        <f>F9*E9</f>
-        <v>62772.160000000003</v>
+        <f t="shared" si="0"/>
+        <v>35995.919999999998</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>44959</v>
+        <v>44954</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E10" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F10" s="6">
-        <v>295.97000000000003</v>
+        <v>3923.26</v>
       </c>
       <c r="G10" s="6">
-        <f>F10*E10</f>
-        <v>4439.55</v>
+        <f t="shared" si="0"/>
+        <v>62772.160000000003</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -715,383 +4386,383 @@
         <v>44959</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="5">
         <v>15</v>
       </c>
-      <c r="E11" s="5">
-        <v>2</v>
-      </c>
       <c r="F11" s="6">
-        <v>2136.39</v>
+        <v>295.97000000000003</v>
       </c>
       <c r="G11" s="6">
-        <f>F11*E11</f>
-        <v>4272.78</v>
+        <f t="shared" si="0"/>
+        <v>4439.55</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>44966</v>
+        <v>44959</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E12" s="5">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F12" s="6">
-        <v>825.2</v>
+        <v>2136.39</v>
       </c>
       <c r="G12" s="6">
-        <f>F12*E12</f>
-        <v>12378</v>
+        <f t="shared" si="0"/>
+        <v>4272.78</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>44967</v>
+        <v>44966</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
       </c>
       <c r="E13" s="5">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F13" s="6">
-        <v>3629.92</v>
+        <v>825.2</v>
       </c>
       <c r="G13" s="6">
-        <f>F13*E13</f>
-        <v>32669.279999999999</v>
+        <f t="shared" si="0"/>
+        <v>12378</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>44971</v>
+        <v>44967</v>
       </c>
       <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="5">
         <v>9</v>
       </c>
-      <c r="C14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" s="5">
-        <v>2</v>
-      </c>
       <c r="F14" s="6">
-        <v>4836.45</v>
+        <v>3629.92</v>
       </c>
       <c r="G14" s="6">
-        <f>F14*E14</f>
-        <v>9672.9</v>
+        <f t="shared" si="0"/>
+        <v>32669.279999999999</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>44973</v>
+        <v>44971</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D15" t="s">
         <v>15</v>
       </c>
       <c r="E15" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F15" s="6">
-        <v>4615.97</v>
+        <v>4836.45</v>
       </c>
       <c r="G15" s="6">
-        <f>F15*E15</f>
-        <v>18463.88</v>
+        <f t="shared" si="0"/>
+        <v>9672.9</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>44975</v>
+        <v>44973</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D16" t="s">
         <v>15</v>
       </c>
       <c r="E16" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F16" s="6">
-        <v>2136.39</v>
+        <v>4615.97</v>
       </c>
       <c r="G16" s="6">
-        <f>F16*E16</f>
-        <v>21363.899999999998</v>
+        <f t="shared" si="0"/>
+        <v>18463.88</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>44977</v>
+        <v>44975</v>
       </c>
       <c r="B17" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E17" s="5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F17" s="6">
-        <v>573.21</v>
+        <v>2136.39</v>
       </c>
       <c r="G17" s="6">
-        <f>F17*E17</f>
-        <v>4012.4700000000003</v>
+        <f t="shared" si="0"/>
+        <v>21363.899999999998</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>44979</v>
+        <v>44977</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E18" s="5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F18" s="6">
-        <v>1390.01</v>
+        <v>573.21</v>
       </c>
       <c r="G18" s="6">
-        <f>F18*E18</f>
-        <v>13900.1</v>
+        <f t="shared" si="0"/>
+        <v>4012.4700000000003</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>44980</v>
+        <v>44979</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="5">
         <v>10</v>
       </c>
-      <c r="E19" s="5">
-        <v>14</v>
-      </c>
       <c r="F19" s="6">
-        <v>1651.42</v>
+        <v>1390.01</v>
       </c>
       <c r="G19" s="6">
-        <f>F19*E19</f>
-        <v>23119.88</v>
+        <f t="shared" si="0"/>
+        <v>13900.1</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>44981</v>
+        <v>44980</v>
       </c>
       <c r="B20" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D20" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="5">
         <v>14</v>
       </c>
-      <c r="E20" s="5">
-        <v>6</v>
-      </c>
       <c r="F20" s="6">
-        <v>2136.39</v>
+        <v>1651.42</v>
       </c>
       <c r="G20" s="6">
-        <f>F20*E20</f>
-        <v>12818.34</v>
+        <f t="shared" si="0"/>
+        <v>23119.88</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>44983</v>
+        <v>44981</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E21" s="5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F21" s="6">
-        <v>1348.91</v>
+        <v>2136.39</v>
       </c>
       <c r="G21" s="6">
-        <f>F21*E21</f>
-        <v>12140.19</v>
+        <f t="shared" si="0"/>
+        <v>12818.34</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>44986</v>
+        <v>44983</v>
       </c>
       <c r="B22" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E22" s="5">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F22" s="6">
-        <v>810.29</v>
+        <v>1348.91</v>
       </c>
       <c r="G22" s="6">
-        <f>F22*E22</f>
-        <v>11344.06</v>
+        <f t="shared" si="0"/>
+        <v>12140.19</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>44990</v>
+        <v>44986</v>
       </c>
       <c r="B23" t="s">
         <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D23" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="5">
         <v>14</v>
       </c>
-      <c r="E23" s="5">
-        <v>3</v>
-      </c>
       <c r="F23" s="6">
-        <v>303.69</v>
+        <v>810.29</v>
       </c>
       <c r="G23" s="6">
-        <f>F23*E23</f>
-        <v>911.06999999999994</v>
+        <f t="shared" si="0"/>
+        <v>11344.06</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>44997</v>
+        <v>44990</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D24" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E24" s="5">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F24" s="6">
-        <v>2166.89</v>
+        <v>303.69</v>
       </c>
       <c r="G24" s="6">
-        <f>F24*E24</f>
-        <v>34670.239999999998</v>
+        <f t="shared" si="0"/>
+        <v>911.06999999999994</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>44999</v>
+        <v>44997</v>
       </c>
       <c r="B25" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E25" s="5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F25" s="6">
-        <v>3318.1</v>
+        <v>2166.89</v>
       </c>
       <c r="G25" s="6">
-        <f>F25*E25</f>
-        <v>56407.7</v>
+        <f t="shared" si="0"/>
+        <v>34670.239999999998</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>45012</v>
+        <v>44999</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D26" t="s">
         <v>8</v>
       </c>
       <c r="E26" s="5">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F26" s="6">
-        <v>3624.34</v>
+        <v>3318.1</v>
       </c>
       <c r="G26" s="6">
-        <f>F26*E26</f>
-        <v>43492.08</v>
+        <f t="shared" si="0"/>
+        <v>56407.7</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1099,220 +4770,220 @@
         <v>45012</v>
       </c>
       <c r="B27" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C27" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D27" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E27" s="5">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F27" s="6">
-        <v>1650.85</v>
+        <v>3624.34</v>
       </c>
       <c r="G27" s="6">
-        <f>F27*E27</f>
-        <v>6603.4</v>
+        <f t="shared" si="0"/>
+        <v>43492.08</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>45016</v>
+        <v>45012</v>
       </c>
       <c r="B28" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D28" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E28" s="5">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F28" s="6">
-        <v>827.4</v>
+        <v>1650.85</v>
       </c>
       <c r="G28" s="6">
-        <f>F28*E28</f>
-        <v>9928.7999999999993</v>
+        <f t="shared" si="0"/>
+        <v>6603.4</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>45020</v>
+        <v>45016</v>
       </c>
       <c r="B29" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D29" t="s">
         <v>10</v>
       </c>
       <c r="E29" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F29" s="6">
-        <v>2643.65</v>
+        <v>827.4</v>
       </c>
       <c r="G29" s="6">
-        <f>F29*E29</f>
-        <v>34367.450000000004</v>
+        <f t="shared" si="0"/>
+        <v>9928.7999999999993</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>45027</v>
+        <v>45020</v>
       </c>
       <c r="B30" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D30" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E30" s="5">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F30" s="6">
-        <v>4513.8999999999996</v>
+        <v>2643.65</v>
       </c>
       <c r="G30" s="6">
-        <f>F30*E30</f>
-        <v>9027.7999999999993</v>
+        <f t="shared" si="0"/>
+        <v>34367.450000000004</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>45029</v>
+        <v>45027</v>
       </c>
       <c r="B31" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E31" s="5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F31" s="6">
-        <v>2787.97</v>
+        <v>4513.8999999999996</v>
       </c>
       <c r="G31" s="6">
-        <f>F31*E31</f>
-        <v>25091.73</v>
+        <f t="shared" si="0"/>
+        <v>9027.7999999999993</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>45036</v>
+        <v>45029</v>
       </c>
       <c r="B32" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E32" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F32" s="6">
-        <v>347.03</v>
+        <v>2787.97</v>
       </c>
       <c r="G32" s="6">
-        <f>F32*E32</f>
-        <v>2429.21</v>
+        <f t="shared" si="0"/>
+        <v>25091.73</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>45037</v>
+        <v>45036</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C33" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D33" t="s">
         <v>15</v>
       </c>
       <c r="E33" s="5">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F33" s="6">
-        <v>717.83</v>
+        <v>347.03</v>
       </c>
       <c r="G33" s="6">
-        <f>F33*E33</f>
-        <v>12203.11</v>
+        <f t="shared" si="0"/>
+        <v>2429.21</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>45040</v>
+        <v>45037</v>
       </c>
       <c r="B34" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D34" t="s">
         <v>15</v>
       </c>
       <c r="E34" s="5">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="F34" s="6">
-        <v>2505.5500000000002</v>
+        <v>717.83</v>
       </c>
       <c r="G34" s="6">
-        <f>F34*E34</f>
-        <v>2505.5500000000002</v>
+        <f t="shared" si="0"/>
+        <v>12203.11</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>45041</v>
+        <v>45040</v>
       </c>
       <c r="B35" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C35" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D35" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E35" s="5">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F35" s="6">
-        <v>345.37</v>
+        <v>2505.5500000000002</v>
       </c>
       <c r="G35" s="6">
-        <f>F35*E35</f>
-        <v>4489.8100000000004</v>
+        <f t="shared" ref="G35:G66" si="1">F35*E35</f>
+        <v>2505.5500000000002</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>45047</v>
+        <v>45041</v>
       </c>
       <c r="B36" t="s">
         <v>9</v>
@@ -1324,326 +4995,326 @@
         <v>10</v>
       </c>
       <c r="E36" s="5">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F36" s="6">
-        <v>3587.68</v>
+        <v>345.37</v>
       </c>
       <c r="G36" s="6">
-        <f>F36*E36</f>
-        <v>25113.759999999998</v>
+        <f t="shared" si="1"/>
+        <v>4489.8100000000004</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>45058</v>
+        <v>45047</v>
       </c>
       <c r="B37" t="s">
         <v>9</v>
       </c>
       <c r="C37" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D37" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E37" s="5">
         <v>7</v>
       </c>
       <c r="F37" s="6">
-        <v>130.11000000000001</v>
+        <v>3587.68</v>
       </c>
       <c r="G37" s="6">
-        <f>F37*E37</f>
-        <v>910.7700000000001</v>
+        <f t="shared" si="1"/>
+        <v>25113.759999999998</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>45062</v>
+        <v>45058</v>
       </c>
       <c r="B38" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D38" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E38" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F38" s="6">
         <v>130.11000000000001</v>
       </c>
       <c r="G38" s="6">
-        <f>F38*E38</f>
-        <v>1170.9900000000002</v>
+        <f t="shared" si="1"/>
+        <v>910.7700000000001</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>45065</v>
+        <v>45062</v>
       </c>
       <c r="B39" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C39" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D39" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E39" s="5">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F39" s="6">
-        <v>3596.45</v>
+        <v>130.11000000000001</v>
       </c>
       <c r="G39" s="6">
-        <f>F39*E39</f>
-        <v>10789.349999999999</v>
+        <f t="shared" si="1"/>
+        <v>1170.9900000000002</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>45068</v>
+        <v>45065</v>
       </c>
       <c r="B40" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C40" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D40" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E40" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F40" s="6">
-        <v>3908.7</v>
+        <v>3596.45</v>
       </c>
       <c r="G40" s="6">
-        <f>F40*E40</f>
-        <v>3908.7</v>
+        <f t="shared" si="1"/>
+        <v>10789.349999999999</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>45069</v>
+        <v>45068</v>
       </c>
       <c r="B41" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C41" t="s">
         <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E41" s="5">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F41" s="6">
-        <v>1882.81</v>
+        <v>3908.7</v>
       </c>
       <c r="G41" s="6">
-        <f>F41*E41</f>
-        <v>24476.53</v>
+        <f t="shared" si="1"/>
+        <v>3908.7</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>45070</v>
+        <v>45069</v>
       </c>
       <c r="B42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" t="s">
+        <v>15</v>
+      </c>
+      <c r="E42" s="5">
         <v>13</v>
       </c>
-      <c r="C42" t="s">
-        <v>19</v>
-      </c>
-      <c r="D42" t="s">
-        <v>14</v>
-      </c>
-      <c r="E42" s="5">
-        <v>9</v>
-      </c>
       <c r="F42" s="6">
-        <v>2136.39</v>
+        <v>1882.81</v>
       </c>
       <c r="G42" s="6">
-        <f>F42*E42</f>
-        <v>19227.509999999998</v>
+        <f t="shared" si="1"/>
+        <v>24476.53</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>45072</v>
+        <v>45070</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
       </c>
       <c r="C43" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D43" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E43" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F43" s="6">
-        <v>482.06</v>
+        <v>2136.39</v>
       </c>
       <c r="G43" s="6">
-        <f>F43*E43</f>
-        <v>3856.48</v>
+        <f t="shared" si="1"/>
+        <v>19227.509999999998</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>45073</v>
+        <v>45072</v>
       </c>
       <c r="B44" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C44" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D44" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E44" s="5">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F44" s="6">
-        <v>3554.54</v>
+        <v>482.06</v>
       </c>
       <c r="G44" s="6">
-        <f>F44*E44</f>
-        <v>71090.8</v>
+        <f t="shared" si="1"/>
+        <v>3856.48</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>45080</v>
+        <v>45073</v>
       </c>
       <c r="B45" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C45" t="s">
+        <v>17</v>
+      </c>
+      <c r="D45" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" s="5">
         <v>20</v>
       </c>
-      <c r="D45" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" s="5">
-        <v>6</v>
-      </c>
       <c r="F45" s="6">
-        <v>2049.16</v>
+        <v>3554.54</v>
       </c>
       <c r="G45" s="6">
-        <f>F45*E45</f>
-        <v>12294.96</v>
+        <f t="shared" si="1"/>
+        <v>71090.8</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>45081</v>
+        <v>45080</v>
       </c>
       <c r="B46" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C46" t="s">
         <v>20</v>
       </c>
       <c r="D46" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E46" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F46" s="6">
-        <v>1168.19</v>
+        <v>2049.16</v>
       </c>
       <c r="G46" s="6">
-        <f>F46*E46</f>
-        <v>2336.38</v>
+        <f t="shared" si="1"/>
+        <v>12294.96</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>45082</v>
+        <v>45081</v>
       </c>
       <c r="B47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C47" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D47" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E47" s="5">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F47" s="6">
-        <v>3923.26</v>
+        <v>1168.19</v>
       </c>
       <c r="G47" s="6">
-        <f>F47*E47</f>
-        <v>39232.600000000006</v>
+        <f t="shared" si="1"/>
+        <v>2336.38</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>45086</v>
+        <v>45082</v>
       </c>
       <c r="B48" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C48" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D48" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E48" s="5">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F48" s="6">
-        <v>4513.8999999999996</v>
+        <v>3923.26</v>
       </c>
       <c r="G48" s="6">
-        <f>F48*E48</f>
-        <v>13541.699999999999</v>
+        <f t="shared" si="1"/>
+        <v>39232.600000000006</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>45091</v>
+        <v>45086</v>
       </c>
       <c r="B49" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C49" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D49" t="s">
         <v>11</v>
       </c>
       <c r="E49" s="5">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F49" s="6">
-        <v>1401.69</v>
+        <v>4513.8999999999996</v>
       </c>
       <c r="G49" s="6">
-        <f>F49*E49</f>
-        <v>19623.66</v>
+        <f t="shared" si="1"/>
+        <v>13541.699999999999</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -1651,23 +5322,23 @@
         <v>45091</v>
       </c>
       <c r="B50" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C50" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D50" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E50" s="5">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F50" s="6">
-        <v>807.99</v>
+        <v>1401.69</v>
       </c>
       <c r="G50" s="6">
-        <f>F50*E50</f>
-        <v>8079.9</v>
+        <f t="shared" si="1"/>
+        <v>19623.66</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -1675,55 +5346,55 @@
         <v>45091</v>
       </c>
       <c r="B51" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C51" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D51" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E51" s="5">
         <v>10</v>
       </c>
       <c r="F51" s="6">
-        <v>2016.18</v>
+        <v>807.99</v>
       </c>
       <c r="G51" s="6">
-        <f>F51*E51</f>
-        <v>20161.8</v>
+        <f t="shared" si="1"/>
+        <v>8079.9</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>45093</v>
+        <v>45091</v>
       </c>
       <c r="B52" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C52" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D52" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E52" s="5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F52" s="6">
-        <v>2505.5500000000002</v>
+        <v>2016.18</v>
       </c>
       <c r="G52" s="6">
-        <f>F52*E52</f>
-        <v>50111</v>
+        <f t="shared" si="1"/>
+        <v>20161.8</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>45097</v>
+        <v>45093</v>
       </c>
       <c r="B53" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C53" t="s">
         <v>18</v>
@@ -1732,86 +5403,86 @@
         <v>15</v>
       </c>
       <c r="E53" s="5">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F53" s="6">
-        <v>573.21</v>
+        <v>2505.5500000000002</v>
       </c>
       <c r="G53" s="6">
-        <f>F53*E53</f>
-        <v>1719.63</v>
+        <f t="shared" si="1"/>
+        <v>50111</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>45101</v>
+        <v>45097</v>
       </c>
       <c r="B54" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C54" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D54" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E54" s="5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F54" s="6">
-        <v>4961.6000000000004</v>
+        <v>573.21</v>
       </c>
       <c r="G54" s="6">
-        <f>F54*E54</f>
-        <v>39692.800000000003</v>
+        <f t="shared" si="1"/>
+        <v>1719.63</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>45106</v>
+        <v>45101</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
       </c>
       <c r="C55" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D55" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E55" s="5">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F55" s="6">
-        <v>1424.69</v>
+        <v>4961.6000000000004</v>
       </c>
       <c r="G55" s="6">
-        <f>F55*E55</f>
-        <v>25644.420000000002</v>
+        <f t="shared" si="1"/>
+        <v>39692.800000000003</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>45111</v>
+        <v>45106</v>
       </c>
       <c r="B56" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C56" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D56" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E56" s="5">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F56" s="6">
-        <v>2873.97</v>
+        <v>1424.69</v>
       </c>
       <c r="G56" s="6">
-        <f>F56*E56</f>
-        <v>20117.789999999997</v>
+        <f t="shared" si="1"/>
+        <v>25644.420000000002</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -1822,188 +5493,188 @@
         <v>12</v>
       </c>
       <c r="C57" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D57" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E57" s="5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F57" s="6">
-        <v>2275.71</v>
+        <v>2873.97</v>
       </c>
       <c r="G57" s="6">
-        <f>F57*E57</f>
-        <v>22757.1</v>
+        <f t="shared" si="1"/>
+        <v>20117.789999999997</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>45114</v>
+        <v>45111</v>
       </c>
       <c r="B58" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C58" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D58" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E58" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F58" s="6">
-        <v>4913.28</v>
+        <v>2275.71</v>
       </c>
       <c r="G58" s="6">
-        <f>F58*E58</f>
-        <v>39306.239999999998</v>
+        <f t="shared" si="1"/>
+        <v>22757.1</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>45117</v>
+        <v>45114</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D59" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E59" s="5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F59" s="6">
-        <v>1650.85</v>
+        <v>4913.28</v>
       </c>
       <c r="G59" s="6">
-        <f>F59*E59</f>
-        <v>18159.349999999999</v>
+        <f t="shared" si="1"/>
+        <v>39306.239999999998</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>45121</v>
+        <v>45117</v>
       </c>
       <c r="B60" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D60" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E60" s="5">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F60" s="6">
-        <v>2415.0700000000002</v>
+        <v>1650.85</v>
       </c>
       <c r="G60" s="6">
-        <f>F60*E60</f>
-        <v>41056.19</v>
+        <f t="shared" si="1"/>
+        <v>18159.349999999999</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>45128</v>
+        <v>45121</v>
       </c>
       <c r="B61" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C61" t="s">
+        <v>19</v>
+      </c>
+      <c r="D61" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" s="5">
         <v>17</v>
       </c>
-      <c r="D61" t="s">
-        <v>15</v>
-      </c>
-      <c r="E61" s="5">
-        <v>20</v>
-      </c>
       <c r="F61" s="6">
-        <v>1882.81</v>
+        <v>2415.0700000000002</v>
       </c>
       <c r="G61" s="6">
-        <f>F61*E61</f>
-        <v>37656.199999999997</v>
+        <f t="shared" si="1"/>
+        <v>41056.19</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>45131</v>
+        <v>45128</v>
       </c>
       <c r="B62" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C62" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D62" t="s">
         <v>15</v>
       </c>
       <c r="E62" s="5">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F62" s="6">
-        <v>4332.25</v>
+        <v>1882.81</v>
       </c>
       <c r="G62" s="6">
-        <f>F62*E62</f>
-        <v>21661.25</v>
+        <f t="shared" si="1"/>
+        <v>37656.199999999997</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>45132</v>
+        <v>45131</v>
       </c>
       <c r="B63" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C63" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D63" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E63" s="5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F63" s="6">
-        <v>130.11000000000001</v>
+        <v>4332.25</v>
       </c>
       <c r="G63" s="6">
-        <f>F63*E63</f>
-        <v>910.7700000000001</v>
+        <f t="shared" si="1"/>
+        <v>21661.25</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>45133</v>
+        <v>45132</v>
       </c>
       <c r="B64" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C64" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D64" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E64" s="5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F64" s="6">
-        <v>1650.85</v>
+        <v>130.11000000000001</v>
       </c>
       <c r="G64" s="6">
-        <f>F64*E64</f>
-        <v>4952.5499999999993</v>
+        <f t="shared" si="1"/>
+        <v>910.7700000000001</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -2011,47 +5682,47 @@
         <v>45133</v>
       </c>
       <c r="B65" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C65" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D65" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E65" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F65" s="6">
-        <v>827.4</v>
+        <v>1650.85</v>
       </c>
       <c r="G65" s="6">
-        <f>F65*E65</f>
-        <v>827.4</v>
+        <f t="shared" si="1"/>
+        <v>4952.5499999999993</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>45140</v>
+        <v>45133</v>
       </c>
       <c r="B66" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C66" t="s">
         <v>21</v>
       </c>
       <c r="D66" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E66" s="5">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F66" s="6">
-        <v>2505.5500000000002</v>
+        <v>827.4</v>
       </c>
       <c r="G66" s="6">
-        <f>F66*E66</f>
-        <v>45099.9</v>
+        <f t="shared" si="1"/>
+        <v>827.4</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -2062,148 +5733,148 @@
         <v>9</v>
       </c>
       <c r="C67" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D67" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E67" s="5">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F67" s="6">
-        <v>807.99</v>
+        <v>2505.5500000000002</v>
       </c>
       <c r="G67" s="6">
-        <f>F67*E67</f>
-        <v>11311.86</v>
+        <f t="shared" ref="G67:G98" si="2">F67*E67</f>
+        <v>45099.9</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>45141</v>
+        <v>45140</v>
       </c>
       <c r="B68" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C68" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D68" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E68" s="5">
         <v>14</v>
       </c>
       <c r="F68" s="6">
-        <v>3139.25</v>
+        <v>807.99</v>
       </c>
       <c r="G68" s="6">
-        <f>F68*E68</f>
-        <v>43949.5</v>
+        <f t="shared" si="2"/>
+        <v>11311.86</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>45144</v>
+        <v>45141</v>
       </c>
       <c r="B69" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C69" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D69" t="s">
         <v>8</v>
       </c>
       <c r="E69" s="5">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F69" s="6">
-        <v>573.21</v>
+        <v>3139.25</v>
       </c>
       <c r="G69" s="6">
-        <f>F69*E69</f>
-        <v>9744.57</v>
+        <f t="shared" si="2"/>
+        <v>43949.5</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>45145</v>
+        <v>45144</v>
       </c>
       <c r="B70" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C70" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D70" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E70" s="5">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F70" s="6">
-        <v>1650.85</v>
+        <v>573.21</v>
       </c>
       <c r="G70" s="6">
-        <f>F70*E70</f>
-        <v>4952.5499999999993</v>
+        <f t="shared" si="2"/>
+        <v>9744.57</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>45146</v>
+        <v>45145</v>
       </c>
       <c r="B71" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C71" t="s">
         <v>21</v>
       </c>
       <c r="D71" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E71" s="5">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F71" s="6">
-        <v>1211.28</v>
+        <v>1650.85</v>
       </c>
       <c r="G71" s="6">
-        <f>F71*E71</f>
-        <v>19380.48</v>
+        <f t="shared" si="2"/>
+        <v>4952.5499999999993</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>45152</v>
+        <v>45146</v>
       </c>
       <c r="B72" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C72" t="s">
         <v>21</v>
       </c>
       <c r="D72" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E72" s="5">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F72" s="6">
-        <v>295.97000000000003</v>
+        <v>1211.28</v>
       </c>
       <c r="G72" s="6">
-        <f>F72*E72</f>
-        <v>3255.67</v>
+        <f t="shared" si="2"/>
+        <v>19380.48</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>45154</v>
+        <v>45152</v>
       </c>
       <c r="B73" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C73" t="s">
         <v>21</v>
@@ -2212,86 +5883,86 @@
         <v>15</v>
       </c>
       <c r="E73" s="5">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F73" s="6">
-        <v>4390.2700000000004</v>
+        <v>295.97000000000003</v>
       </c>
       <c r="G73" s="6">
-        <f>F73*E73</f>
-        <v>74634.590000000011</v>
+        <f t="shared" si="2"/>
+        <v>3255.67</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>45155</v>
+        <v>45154</v>
       </c>
       <c r="B74" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C74" t="s">
         <v>21</v>
       </c>
       <c r="D74" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E74" s="5">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F74" s="6">
-        <v>2643.65</v>
+        <v>4390.2700000000004</v>
       </c>
       <c r="G74" s="6">
-        <f>F74*E74</f>
-        <v>52873</v>
+        <f t="shared" si="2"/>
+        <v>74634.590000000011</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>45161</v>
+        <v>45155</v>
       </c>
       <c r="B75" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C75" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D75" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E75" s="5">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F75" s="6">
-        <v>4615.97</v>
+        <v>2643.65</v>
       </c>
       <c r="G75" s="6">
-        <f>F75*E75</f>
-        <v>73855.520000000004</v>
+        <f t="shared" si="2"/>
+        <v>52873</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>45169</v>
+        <v>45161</v>
       </c>
       <c r="B76" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C76" t="s">
         <v>19</v>
       </c>
       <c r="D76" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E76" s="5">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F76" s="6">
-        <v>3908.7</v>
+        <v>4615.97</v>
       </c>
       <c r="G76" s="6">
-        <f>F76*E76</f>
-        <v>23452.199999999997</v>
+        <f t="shared" si="2"/>
+        <v>73855.520000000004</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -2299,7 +5970,7 @@
         <v>45169</v>
       </c>
       <c r="B77" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C77" t="s">
         <v>19</v>
@@ -2308,70 +5979,70 @@
         <v>14</v>
       </c>
       <c r="E77" s="5">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F77" s="6">
-        <v>1651.42</v>
+        <v>3908.7</v>
       </c>
       <c r="G77" s="6">
-        <f>F77*E77</f>
-        <v>18165.620000000003</v>
+        <f t="shared" si="2"/>
+        <v>23452.199999999997</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>45173</v>
+        <v>45169</v>
       </c>
       <c r="B78" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C78" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D78" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E78" s="5">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F78" s="6">
-        <v>3110.71</v>
+        <v>1651.42</v>
       </c>
       <c r="G78" s="6">
-        <f>F78*E78</f>
-        <v>15553.55</v>
+        <f t="shared" si="2"/>
+        <v>18165.620000000003</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>45175</v>
+        <v>45173</v>
       </c>
       <c r="B79" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C79" t="s">
         <v>20</v>
       </c>
       <c r="D79" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E79" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F79" s="6">
-        <v>1168.19</v>
+        <v>3110.71</v>
       </c>
       <c r="G79" s="6">
-        <f>F79*E79</f>
-        <v>4672.76</v>
+        <f t="shared" si="2"/>
+        <v>15553.55</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>45177</v>
+        <v>45175</v>
       </c>
       <c r="B80" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C80" t="s">
         <v>20</v>
@@ -2380,38 +6051,38 @@
         <v>10</v>
       </c>
       <c r="E80" s="5">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F80" s="6">
-        <v>2239.29</v>
+        <v>1168.19</v>
       </c>
       <c r="G80" s="6">
-        <f>F80*E80</f>
-        <v>42546.51</v>
+        <f t="shared" si="2"/>
+        <v>4672.76</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>45182</v>
+        <v>45177</v>
       </c>
       <c r="B81" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C81" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D81" t="s">
         <v>10</v>
       </c>
       <c r="E81" s="5">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F81" s="6">
-        <v>3822.16</v>
+        <v>2239.29</v>
       </c>
       <c r="G81" s="6">
-        <f>F81*E81</f>
-        <v>30577.279999999999</v>
+        <f t="shared" si="2"/>
+        <v>42546.51</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -2419,71 +6090,71 @@
         <v>45182</v>
       </c>
       <c r="B82" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C82" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D82" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E82" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F82" s="6">
-        <v>1168.19</v>
+        <v>3822.16</v>
       </c>
       <c r="G82" s="6">
-        <f>F82*E82</f>
-        <v>5840.9500000000007</v>
+        <f t="shared" si="2"/>
+        <v>30577.279999999999</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>45187</v>
+        <v>45182</v>
       </c>
       <c r="B83" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C83" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D83" t="s">
         <v>11</v>
       </c>
       <c r="E83" s="5">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F83" s="6">
-        <v>4513.8999999999996</v>
+        <v>1168.19</v>
       </c>
       <c r="G83" s="6">
-        <f>F83*E83</f>
-        <v>63194.599999999991</v>
+        <f t="shared" si="2"/>
+        <v>5840.9500000000007</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>45188</v>
+        <v>45187</v>
       </c>
       <c r="B84" t="s">
         <v>9</v>
       </c>
       <c r="C84" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D84" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E84" s="5">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F84" s="6">
-        <v>2077.83</v>
+        <v>4513.8999999999996</v>
       </c>
       <c r="G84" s="6">
-        <f>F84*E84</f>
-        <v>16622.64</v>
+        <f t="shared" si="2"/>
+        <v>63194.599999999991</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -2491,143 +6162,143 @@
         <v>45188</v>
       </c>
       <c r="B85" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C85" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D85" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E85" s="5">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F85" s="6">
-        <v>4587.28</v>
+        <v>2077.83</v>
       </c>
       <c r="G85" s="6">
-        <f>F85*E85</f>
-        <v>13761.84</v>
+        <f t="shared" si="2"/>
+        <v>16622.64</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>45194</v>
+        <v>45188</v>
       </c>
       <c r="B86" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C86" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D86" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E86" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F86" s="6">
-        <v>90.35</v>
+        <v>4587.28</v>
       </c>
       <c r="G86" s="6">
-        <f>F86*E86</f>
-        <v>180.7</v>
+        <f t="shared" si="2"/>
+        <v>13761.84</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>45195</v>
+        <v>45194</v>
       </c>
       <c r="B87" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C87" t="s">
         <v>17</v>
       </c>
       <c r="D87" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E87" s="5">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F87" s="6">
-        <v>550.23</v>
+        <v>90.35</v>
       </c>
       <c r="G87" s="6">
-        <f>F87*E87</f>
-        <v>7152.99</v>
+        <f t="shared" si="2"/>
+        <v>180.7</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>45196</v>
+        <v>45195</v>
       </c>
       <c r="B88" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C88" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D88" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E88" s="5">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F88" s="6">
-        <v>3318.1</v>
+        <v>550.23</v>
       </c>
       <c r="G88" s="6">
-        <f>F88*E88</f>
-        <v>26544.799999999999</v>
+        <f t="shared" si="2"/>
+        <v>7152.99</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>45205</v>
+        <v>45196</v>
       </c>
       <c r="B89" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C89" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D89" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E89" s="5">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F89" s="6">
-        <v>2450.65</v>
+        <v>3318.1</v>
       </c>
       <c r="G89" s="6">
-        <f>F89*E89</f>
-        <v>44111.700000000004</v>
+        <f t="shared" si="2"/>
+        <v>26544.799999999999</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>45207</v>
+        <v>45205</v>
       </c>
       <c r="B90" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C90" t="s">
         <v>21</v>
       </c>
       <c r="D90" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E90" s="5">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F90" s="6">
-        <v>1168.19</v>
+        <v>2450.65</v>
       </c>
       <c r="G90" s="6">
-        <f>F90*E90</f>
-        <v>18691.04</v>
+        <f t="shared" si="2"/>
+        <v>44111.700000000004</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -2641,46 +6312,46 @@
         <v>21</v>
       </c>
       <c r="D91" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E91" s="5">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F91" s="6">
-        <v>1650.85</v>
+        <v>1168.19</v>
       </c>
       <c r="G91" s="6">
-        <f>F91*E91</f>
-        <v>14857.65</v>
+        <f t="shared" si="2"/>
+        <v>18691.04</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>45211</v>
+        <v>45207</v>
       </c>
       <c r="B92" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C92" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D92" t="s">
         <v>11</v>
       </c>
       <c r="E92" s="5">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F92" s="6">
-        <v>1168.19</v>
+        <v>1650.85</v>
       </c>
       <c r="G92" s="6">
-        <f>F92*E92</f>
-        <v>5840.9500000000007</v>
+        <f t="shared" si="2"/>
+        <v>14857.65</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>45213</v>
+        <v>45211</v>
       </c>
       <c r="B93" t="s">
         <v>9</v>
@@ -2689,22 +6360,22 @@
         <v>20</v>
       </c>
       <c r="D93" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E93" s="5">
         <v>5</v>
       </c>
       <c r="F93" s="6">
-        <v>573.21</v>
+        <v>1168.19</v>
       </c>
       <c r="G93" s="6">
-        <f>F93*E93</f>
-        <v>2866.05</v>
+        <f t="shared" si="2"/>
+        <v>5840.9500000000007</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>45218</v>
+        <v>45213</v>
       </c>
       <c r="B94" t="s">
         <v>9</v>
@@ -2716,14 +6387,14 @@
         <v>10</v>
       </c>
       <c r="E94" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F94" s="6">
-        <v>3587.68</v>
+        <v>573.21</v>
       </c>
       <c r="G94" s="6">
-        <f>F94*E94</f>
-        <v>21526.079999999998</v>
+        <f t="shared" si="2"/>
+        <v>2866.05</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -2731,76 +6402,76 @@
         <v>45218</v>
       </c>
       <c r="B95" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C95" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D95" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E95" s="5">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F95" s="6">
-        <v>2016.18</v>
+        <v>3587.68</v>
       </c>
       <c r="G95" s="6">
-        <f>F95*E95</f>
-        <v>34275.06</v>
+        <f t="shared" si="2"/>
+        <v>21526.079999999998</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>45219</v>
+        <v>45218</v>
       </c>
       <c r="B96" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C96" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D96" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E96" s="5">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="F96" s="6">
-        <v>4499.49</v>
+        <v>2016.18</v>
       </c>
       <c r="G96" s="6">
-        <f>F96*E96</f>
-        <v>8998.98</v>
+        <f t="shared" si="2"/>
+        <v>34275.06</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>45225</v>
+        <v>45219</v>
       </c>
       <c r="B97" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C97" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D97" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E97" s="5">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F97" s="6">
-        <v>2465.4499999999998</v>
+        <v>4499.49</v>
       </c>
       <c r="G97" s="6">
-        <f>F97*E97</f>
-        <v>27119.949999999997</v>
+        <f t="shared" si="2"/>
+        <v>8998.98</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>45226</v>
+        <v>45225</v>
       </c>
       <c r="B98" t="s">
         <v>12</v>
@@ -2809,73 +6480,73 @@
         <v>18</v>
       </c>
       <c r="D98" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E98" s="5">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F98" s="6">
-        <v>313.20999999999998</v>
+        <v>2465.4499999999998</v>
       </c>
       <c r="G98" s="6">
-        <f>F98*E98</f>
-        <v>4384.9399999999996</v>
+        <f t="shared" si="2"/>
+        <v>27119.949999999997</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>45228</v>
+        <v>45226</v>
       </c>
       <c r="B99" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C99" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D99" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E99" s="5">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F99" s="6">
-        <v>1108.71</v>
+        <v>313.20999999999998</v>
       </c>
       <c r="G99" s="6">
-        <f>F99*E99</f>
-        <v>21065.49</v>
+        <f t="shared" ref="G99:G130" si="3">F99*E99</f>
+        <v>4384.9399999999996</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>45234</v>
+        <v>45228</v>
       </c>
       <c r="B100" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C100" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D100" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E100" s="5">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F100" s="6">
-        <v>179.65</v>
+        <v>1108.71</v>
       </c>
       <c r="G100" s="6">
-        <f>F100*E100</f>
-        <v>3054.05</v>
+        <f t="shared" si="3"/>
+        <v>21065.49</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>45248</v>
+        <v>45234</v>
       </c>
       <c r="B101" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C101" t="s">
         <v>20</v>
@@ -2884,38 +6555,38 @@
         <v>14</v>
       </c>
       <c r="E101" s="5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F101" s="6">
-        <v>1651.42</v>
+        <v>179.65</v>
       </c>
       <c r="G101" s="6">
-        <f>F101*E101</f>
-        <v>24771.300000000003</v>
+        <f t="shared" si="3"/>
+        <v>3054.05</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>45250</v>
+        <v>45248</v>
       </c>
       <c r="B102" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C102" t="s">
         <v>20</v>
       </c>
       <c r="D102" t="s">
+        <v>14</v>
+      </c>
+      <c r="E102" s="5">
         <v>15</v>
       </c>
-      <c r="E102" s="5">
-        <v>2</v>
-      </c>
       <c r="F102" s="6">
-        <v>827.4</v>
+        <v>1651.42</v>
       </c>
       <c r="G102" s="6">
-        <f>F102*E102</f>
-        <v>1654.8</v>
+        <f t="shared" si="3"/>
+        <v>24771.300000000003</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -2923,76 +6594,76 @@
         <v>45250</v>
       </c>
       <c r="B103" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C103" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D103" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E103" s="5">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F103" s="6">
-        <v>702.91</v>
+        <v>827.4</v>
       </c>
       <c r="G103" s="6">
-        <f>F103*E103</f>
-        <v>7732.0099999999993</v>
+        <f t="shared" si="3"/>
+        <v>1654.8</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>45251</v>
+        <v>45250</v>
       </c>
       <c r="B104" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C104" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D104" t="s">
+        <v>8</v>
+      </c>
+      <c r="E104" s="5">
         <v>11</v>
       </c>
-      <c r="E104" s="5">
-        <v>12</v>
-      </c>
       <c r="F104" s="6">
-        <v>3318.1</v>
+        <v>702.91</v>
       </c>
       <c r="G104" s="6">
-        <f>F104*E104</f>
-        <v>39817.199999999997</v>
+        <f t="shared" si="3"/>
+        <v>7732.0099999999993</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>45253</v>
+        <v>45251</v>
       </c>
       <c r="B105" t="s">
+        <v>7</v>
+      </c>
+      <c r="C105" t="s">
+        <v>17</v>
+      </c>
+      <c r="D105" t="s">
+        <v>11</v>
+      </c>
+      <c r="E105" s="5">
         <v>12</v>
       </c>
-      <c r="C105" t="s">
-        <v>19</v>
-      </c>
-      <c r="D105" t="s">
-        <v>15</v>
-      </c>
-      <c r="E105" s="5">
-        <v>4</v>
-      </c>
       <c r="F105" s="6">
-        <v>827.4</v>
+        <v>3318.1</v>
       </c>
       <c r="G105" s="6">
-        <f>F105*E105</f>
-        <v>3309.6</v>
+        <f t="shared" si="3"/>
+        <v>39817.199999999997</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>45261</v>
+        <v>45253</v>
       </c>
       <c r="B106" t="s">
         <v>12</v>
@@ -3001,89 +6672,89 @@
         <v>19</v>
       </c>
       <c r="D106" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E106" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F106" s="6">
-        <v>4499.49</v>
+        <v>827.4</v>
       </c>
       <c r="G106" s="6">
-        <f>F106*E106</f>
-        <v>22497.449999999997</v>
+        <f t="shared" si="3"/>
+        <v>3309.6</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>45263</v>
+        <v>45261</v>
       </c>
       <c r="B107" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C107" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D107" t="s">
         <v>10</v>
       </c>
       <c r="E107" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F107" s="6">
-        <v>3218.22</v>
+        <v>4499.49</v>
       </c>
       <c r="G107" s="6">
-        <f>F107*E107</f>
-        <v>19309.32</v>
+        <f t="shared" si="3"/>
+        <v>22497.449999999997</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>45264</v>
+        <v>45263</v>
       </c>
       <c r="B108" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C108" t="s">
         <v>17</v>
       </c>
       <c r="D108" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E108" s="5">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F108" s="6">
-        <v>1417.08</v>
+        <v>3218.22</v>
       </c>
       <c r="G108" s="6">
-        <f>F108*E108</f>
-        <v>17004.96</v>
+        <f t="shared" si="3"/>
+        <v>19309.32</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>45266</v>
+        <v>45264</v>
       </c>
       <c r="B109" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C109" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D109" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E109" s="5">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F109" s="6">
-        <v>573.21</v>
+        <v>1417.08</v>
       </c>
       <c r="G109" s="6">
-        <f>F109*E109</f>
-        <v>573.21</v>
+        <f t="shared" si="3"/>
+        <v>17004.96</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -3091,167 +6762,167 @@
         <v>45266</v>
       </c>
       <c r="B110" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C110" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D110" t="s">
         <v>10</v>
       </c>
       <c r="E110" s="5">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F110" s="6">
         <v>573.21</v>
       </c>
       <c r="G110" s="6">
-        <f>F110*E110</f>
-        <v>8598.1500000000015</v>
+        <f t="shared" si="3"/>
+        <v>573.21</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>45268</v>
+        <v>45266</v>
       </c>
       <c r="B111" t="s">
         <v>9</v>
       </c>
       <c r="C111" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D111" t="s">
+        <v>10</v>
+      </c>
+      <c r="E111" s="5">
         <v>15</v>
       </c>
-      <c r="E111" s="5">
-        <v>19</v>
-      </c>
       <c r="F111" s="6">
-        <v>2136.39</v>
+        <v>573.21</v>
       </c>
       <c r="G111" s="6">
-        <f>F111*E111</f>
-        <v>40591.409999999996</v>
+        <f t="shared" si="3"/>
+        <v>8598.1500000000015</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>45271</v>
+        <v>45268</v>
       </c>
       <c r="B112" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C112" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D112" t="s">
         <v>15</v>
       </c>
       <c r="E112" s="5">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F112" s="6">
-        <v>1966.9</v>
+        <v>2136.39</v>
       </c>
       <c r="G112" s="6">
-        <f>F112*E112</f>
-        <v>15735.2</v>
+        <f t="shared" si="3"/>
+        <v>40591.409999999996</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <v>45273</v>
+        <v>45271</v>
       </c>
       <c r="B113" t="s">
         <v>13</v>
       </c>
       <c r="C113" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D113" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E113" s="5">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F113" s="6">
-        <v>1651.42</v>
+        <v>1966.9</v>
       </c>
       <c r="G113" s="6">
-        <f>F113*E113</f>
-        <v>26422.720000000001</v>
+        <f t="shared" si="3"/>
+        <v>15735.2</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>45274</v>
+        <v>45273</v>
       </c>
       <c r="B114" t="s">
         <v>13</v>
       </c>
       <c r="C114" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D114" t="s">
         <v>14</v>
       </c>
       <c r="E114" s="5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F114" s="6">
-        <v>827.4</v>
+        <v>1651.42</v>
       </c>
       <c r="G114" s="6">
-        <f>F114*E114</f>
-        <v>14065.8</v>
+        <f t="shared" si="3"/>
+        <v>26422.720000000001</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <v>45276</v>
+        <v>45274</v>
       </c>
       <c r="B115" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C115" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D115" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E115" s="5">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F115" s="6">
-        <v>2649.97</v>
+        <v>827.4</v>
       </c>
       <c r="G115" s="6">
-        <f>F115*E115</f>
-        <v>7949.91</v>
+        <f t="shared" si="3"/>
+        <v>14065.8</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <v>45280</v>
+        <v>45276</v>
       </c>
       <c r="B116" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C116" t="s">
         <v>20</v>
       </c>
       <c r="D116" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E116" s="5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F116" s="6">
-        <v>3523.1</v>
+        <v>2649.97</v>
       </c>
       <c r="G116" s="6">
-        <f>F116*E116</f>
-        <v>31707.899999999998</v>
+        <f t="shared" si="3"/>
+        <v>7949.91</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -3259,137 +6930,322 @@
         <v>45280</v>
       </c>
       <c r="B117" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C117" t="s">
         <v>20</v>
       </c>
       <c r="D117" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E117" s="5">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F117" s="6">
-        <v>1650.85</v>
+        <v>3523.1</v>
       </c>
       <c r="G117" s="6">
-        <f>F117*E117</f>
-        <v>4952.5499999999993</v>
+        <f t="shared" si="3"/>
+        <v>31707.899999999998</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
-        <v>45284</v>
+        <v>45280</v>
       </c>
       <c r="B118" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C118" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D118" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E118" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F118" s="6">
-        <v>670.54</v>
+        <v>1650.85</v>
       </c>
       <c r="G118" s="6">
-        <f>F118*E118</f>
-        <v>3352.7</v>
+        <f t="shared" si="3"/>
+        <v>4952.5499999999993</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
-        <v>45286</v>
+        <v>45284</v>
       </c>
       <c r="B119" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C119" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D119" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E119" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F119" s="6">
-        <v>4499.49</v>
+        <v>670.54</v>
       </c>
       <c r="G119" s="6">
-        <f>F119*E119</f>
-        <v>4499.49</v>
+        <f t="shared" si="3"/>
+        <v>3352.7</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <v>45288</v>
+        <v>45286</v>
       </c>
       <c r="B120" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C120" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D120" t="s">
         <v>10</v>
       </c>
       <c r="E120" s="5">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="F120" s="6">
-        <v>380.24</v>
+        <v>4499.49</v>
       </c>
       <c r="G120" s="6">
-        <f>F120*E120</f>
-        <v>7224.56</v>
+        <f t="shared" si="3"/>
+        <v>4499.49</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
-        <v>45291</v>
+        <v>45288</v>
       </c>
       <c r="B121" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C121" t="s">
         <v>20</v>
       </c>
       <c r="D121" t="s">
+        <v>10</v>
+      </c>
+      <c r="E121" s="5">
+        <v>19</v>
+      </c>
+      <c r="F121" s="6">
+        <v>380.24</v>
+      </c>
+      <c r="G121" s="6">
+        <f t="shared" si="3"/>
+        <v>7224.56</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
+        <v>45291</v>
+      </c>
+      <c r="B122" t="s">
+        <v>7</v>
+      </c>
+      <c r="C122" t="s">
+        <v>20</v>
+      </c>
+      <c r="D122" t="s">
         <v>15</v>
       </c>
-      <c r="E121" s="5">
+      <c r="E122" s="5">
         <v>10</v>
       </c>
-      <c r="F121" s="6">
+      <c r="F122" s="6">
         <v>313.20999999999998</v>
       </c>
-      <c r="G121" s="6">
-        <f>F121*E121</f>
+      <c r="G122" s="6">
+        <f t="shared" si="3"/>
         <v>3132.1</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F122" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G122" s="6">
-        <f>SUM(G2:G121)</f>
-        <v>2341703.4100000015</v>
-      </c>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F123" s="7"/>
+      <c r="G123" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G122" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G122">
-      <sortCondition ref="A1:A122"/>
+  <autoFilter ref="A2:G123" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G123">
+      <sortCondition ref="A2:A123"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56EE8C4F-4510-4B71-BD29-9F0FBEB655ED}">
+  <dimension ref="B5:E21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" s="6">
+        <f>SUM('Dados Tratados'!G3:G122)</f>
+        <v>2341703.4100000015</v>
+      </c>
+      <c r="C6" s="5">
+        <f>SUM('Dados Tratados'!E3:E122)</f>
+        <v>1180</v>
+      </c>
+      <c r="D6" s="6">
+        <f>B6/C6</f>
+        <v>1984.4944152542387</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="11">
+        <v>199573.19000000003</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="11">
+        <v>169251.27</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B11" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="11">
+        <v>163357.34999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B12" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="11">
+        <v>90114.66</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B13" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="11">
+        <v>160544.88999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B14" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="11">
+        <v>232438.85</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B15" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="11">
+        <v>207404.83999999997</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="11">
+        <v>380675.46000000008</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="11">
+        <v>226648.61999999997</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="11">
+        <v>203737.89</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="11">
+        <v>80338.960000000006</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="11">
+        <v>227617.42999999996</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="6">
+        <v>2341703.41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAD78F76-FE33-44D5-B879-616F6349FAC8}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/data/dados_tratados.xlsx
+++ b/data/dados_tratados.xlsx
@@ -1,28 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaike\OneDrive\Documentos\GitHub\analise-vendas-excel\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{248DAA35-834A-496F-92BF-356043426EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C2FF5F0-E2C0-4FA5-828E-410EC354968C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dados Tratados" sheetId="1" r:id="rId1"/>
-    <sheet name="Análises" sheetId="2" r:id="rId2"/>
-    <sheet name="Dashboard" sheetId="3" r:id="rId3"/>
+    <sheet name="Detalhes1" sheetId="4" state="hidden" r:id="rId2"/>
+    <sheet name="Análises" sheetId="2" r:id="rId3"/>
+    <sheet name="Dashboard" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dados Tratados'!$A$2:$G$123</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="12" r:id="rId4"/>
+    <pivotCache cacheId="12" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="48">
   <si>
     <t>Data</t>
   </si>
@@ -180,6 +181,15 @@
   <si>
     <t>Evolução do Faturamento Mensal</t>
   </si>
+  <si>
+    <t>1 . O faturamento mensal atingiu seu pico em agosto (R$380.675,46), indicando possíveis influências de campanhas comerciais ou aumento pontual na demanda.</t>
+  </si>
+  <si>
+    <t>2. Foram observadas quedas significativas em abril (R$ 90.114,66) e novembro (R$ 80.338,96), possivelmente relacionadas à fatores sazonais.</t>
+  </si>
+  <si>
+    <t>Detalhes do Soma de Receita - Meses (Data): Jun</t>
+  </si>
 </sst>
 </file>
 
@@ -260,7 +270,10 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="28">
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -441,11 +454,11 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
+              <a:rPr lang="en-US" b="1"/>
               <a:t>Evolução do Faturamento</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
+              <a:rPr lang="en-US" b="1" baseline="0"/>
               <a:t> Mensal em 2023</a:t>
             </a:r>
           </a:p>
@@ -788,7 +801,9 @@
       <c:spPr>
         <a:noFill/>
         <a:ln>
-          <a:noFill/>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
         </a:ln>
         <a:effectLst/>
       </c:spPr>
@@ -1502,16 +1517,16 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>485775</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>4762</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>539</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>184479</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>359973</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:rowOff>539</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3729,13 +3744,13 @@
     <dataField name="Soma de Receita" fld="6" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="26">
+    <format dxfId="27">
       <pivotArea field="8" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="25">
+    <format dxfId="26">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="23">
+    <format dxfId="24">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="8" count="1">
@@ -3744,7 +3759,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="21">
+    <format dxfId="22">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="8" count="1">
@@ -3753,7 +3768,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="19">
+    <format dxfId="20">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="8" count="1">
@@ -3762,7 +3777,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="17">
+    <format dxfId="18">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="8" count="1">
@@ -3771,7 +3786,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="15">
+    <format dxfId="16">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="8" count="1">
@@ -3780,7 +3795,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="13">
+    <format dxfId="14">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="8" count="1">
@@ -3789,7 +3804,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="11">
+    <format dxfId="12">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="8" count="1">
@@ -3798,7 +3813,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="9">
+    <format dxfId="10">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="8" count="1">
@@ -3807,7 +3822,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="7">
+    <format dxfId="8">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="8" count="1">
@@ -3816,7 +3831,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="5">
+    <format dxfId="6">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="8" count="1">
@@ -3825,7 +3840,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="3">
+    <format dxfId="4">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="8" count="1">
@@ -3834,7 +3849,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="1">
+    <format dxfId="2">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="8" count="1">
@@ -3865,6 +3880,22 @@
     </ext>
   </extLst>
 </pivotTableDefinition>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B48DC75E-31D2-4CE8-8832-F3B6414A414D}" name="Tabela1" displayName="Tabela1" ref="A3:G14" totalsRowShown="0">
+  <autoFilter ref="A3:G14" xr:uid="{B48DC75E-31D2-4CE8-8832-F3B6414A414D}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{8F263DA3-B4AA-4FC5-8D25-5E8A900EC0AA}" name="Data" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{A54017AF-4388-4875-B62D-5100BEAF89A6}" name="Produto"/>
+    <tableColumn id="3" xr3:uid="{A73FF01D-D171-4AB8-B5B6-6C7DBE5D854F}" name="Região"/>
+    <tableColumn id="4" xr3:uid="{41F6B357-11B5-4542-BDA6-26F1631E5636}" name="Vendedor"/>
+    <tableColumn id="5" xr3:uid="{B46023A8-1EDD-465D-A154-6B882610EA59}" name="Quantidade"/>
+    <tableColumn id="6" xr3:uid="{C0E3DBF6-19EE-447E-95AB-7761F6843B93}" name="Preço Unitário"/>
+    <tableColumn id="7" xr3:uid="{746F4173-60BF-4272-A071-867538FA3E6F}" name="Receita"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7085,17 +7116,330 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C90171A-A64B-4A47-9F0F-E9F4B66FA6AC}">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>45080</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+      <c r="F4">
+        <v>2049.16</v>
+      </c>
+      <c r="G4">
+        <v>12294.96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>45081</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>1168.19</v>
+      </c>
+      <c r="G5">
+        <v>2336.38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>45082</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>3923.26</v>
+      </c>
+      <c r="G6">
+        <v>39232.600000000006</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>45086</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>4513.8999999999996</v>
+      </c>
+      <c r="G7">
+        <v>13541.699999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>45091</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8">
+        <v>10</v>
+      </c>
+      <c r="F8">
+        <v>2016.18</v>
+      </c>
+      <c r="G8">
+        <v>20161.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>45091</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+      <c r="F9">
+        <v>807.99</v>
+      </c>
+      <c r="G9">
+        <v>8079.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>45091</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10">
+        <v>14</v>
+      </c>
+      <c r="F10">
+        <v>1401.69</v>
+      </c>
+      <c r="G10">
+        <v>19623.66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>45093</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11">
+        <v>20</v>
+      </c>
+      <c r="F11">
+        <v>2505.5500000000002</v>
+      </c>
+      <c r="G11">
+        <v>50111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>45097</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+      <c r="F12">
+        <v>573.21</v>
+      </c>
+      <c r="G12">
+        <v>1719.63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>45101</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13">
+        <v>8</v>
+      </c>
+      <c r="F13">
+        <v>4961.6000000000004</v>
+      </c>
+      <c r="G13">
+        <v>39692.800000000003</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>45106</v>
+      </c>
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14">
+        <v>18</v>
+      </c>
+      <c r="F14">
+        <v>1424.69</v>
+      </c>
+      <c r="G14">
+        <v>25644.420000000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56EE8C4F-4510-4B71-BD29-9F0FBEB655ED}">
-  <dimension ref="B5:E21"/>
+  <dimension ref="B4:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.5703125" customWidth="1"/>
+    <col min="7" max="7" width="31.140625" customWidth="1"/>
+    <col min="14" max="14" width="12.28515625" customWidth="1"/>
+    <col min="15" max="15" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="G4" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>40</v>
       </c>
@@ -7105,11 +7449,11 @@
       <c r="D5" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="6">
         <f>SUM('Dados Tratados'!G3:G122)</f>
         <v>2341703.4100000015</v>
@@ -7122,8 +7466,11 @@
         <f>B6/C6</f>
         <v>1984.4944152542387</v>
       </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="10" t="s">
         <v>43</v>
       </c>
@@ -7131,7 +7478,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
         <v>28</v>
       </c>
@@ -7139,7 +7486,7 @@
         <v>199573.19000000003</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="9" t="s">
         <v>29</v>
       </c>
@@ -7147,7 +7494,7 @@
         <v>169251.27</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
         <v>30</v>
       </c>
@@ -7155,7 +7502,7 @@
         <v>163357.34999999998</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="9" t="s">
         <v>31</v>
       </c>
@@ -7163,7 +7510,7 @@
         <v>90114.66</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>32</v>
       </c>
@@ -7171,7 +7518,7 @@
         <v>160544.88999999998</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="9" t="s">
         <v>33</v>
       </c>
@@ -7179,7 +7526,7 @@
         <v>232438.85</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
         <v>34</v>
       </c>
@@ -7187,7 +7534,7 @@
         <v>207404.83999999997</v>
       </c>
     </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
         <v>35</v>
       </c>
@@ -7241,7 +7588,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAD78F76-FE33-44D5-B879-616F6349FAC8}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
